--- a/rapporten/prijsrapport-NL-2026-05-16.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="158">
   <si>
     <t>Product</t>
   </si>
@@ -479,6 +479,12 @@
   </si>
   <si>
     <t>8715658360018</t>
+  </si>
+  <si>
+    <t>Hello Kitty Club Parfum set 3 stuks voor kinderen - Meisjes</t>
+  </si>
+  <si>
+    <t>8721055493327</t>
   </si>
 </sst>
 </file>
@@ -870,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4653,6 +4659,32 @@
         <v>10</v>
       </c>
     </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>156</v>
+      </c>
+      <c r="B146" t="s">
+        <v>157</v>
+      </c>
+      <c r="C146" s="1">
+        <v>19.99</v>
+      </c>
+      <c r="D146" s="1">
+        <v>19.95</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F146" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="1">
+        <v>19.95</v>
+      </c>
+      <c r="H146" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/rapporten/prijsrapport-NL-2026-05-16.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="309">
   <si>
     <t>Product</t>
   </si>
@@ -37,445 +37,898 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Creation Lamis Catsuit Man - Topparfum voor de zelfverzekerde man - 3 stuks</t>
+  </si>
+  <si>
     <t>8719326174709</t>
   </si>
   <si>
-    <t>1762224</t>
+    <t>Koopjesfun.nl</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
-    <t>1692530</t>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
   </si>
   <si>
     <t>7640158817018</t>
   </si>
   <si>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>6291012000261</t>
+  </si>
+  <si>
+    <t>Dorsh</t>
+  </si>
+  <si>
+    <t>SENTIO FEESTDAGEN PINK - Wonderful - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492733</t>
   </si>
   <si>
+    <t>Bubble Bliss - Giftset - Unicorn Dreamy Glitterwings - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055494041</t>
   </si>
   <si>
+    <t>Bubble Bliss - Giftset - You're Flamazing - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055494003</t>
   </si>
   <si>
+    <t>Sentio Sway With Me Eau de Parfum For Her 50ml</t>
+  </si>
+  <si>
     <t>8721055491767</t>
   </si>
   <si>
+    <t>Sentio Love &amp; Casual for Everyone Eau de Parfum Spray 100 ml</t>
+  </si>
+  <si>
     <t>8721055493747</t>
   </si>
   <si>
+    <t>NG Axure Sport Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214758325</t>
   </si>
   <si>
+    <t>Omerta - Big The Fragrance Release - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370093</t>
   </si>
   <si>
+    <t>Atelier Privee Mistical France Unisex - Sugar Fortune - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
     <t>8721055495765</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Sweet Leopard Pink - Eau de Parfum + Bodymist - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055496373</t>
   </si>
   <si>
+    <t>Sentio Rose Espresso Unisex Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8721055491415</t>
   </si>
   <si>
+    <t>Creation Lamis Arrivederci Giftset</t>
+  </si>
+  <si>
     <t>6291012002692</t>
   </si>
   <si>
+    <t>Real Time - Tempting Rumors - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658361619</t>
   </si>
   <si>
+    <t>Street Looks - Fleurette - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658013006</t>
   </si>
   <si>
+    <t>Real Time Wild Action Elixir men edt 100 ml</t>
+  </si>
+  <si>
     <t>8715658350637</t>
   </si>
   <si>
+    <t>Omerta Pure E-motion Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658997436</t>
   </si>
   <si>
+    <t>Omerta Express Sensualite Frivole 100ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8715658380238</t>
   </si>
   <si>
+    <t>Omerta Liquid Marble Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658370147</t>
   </si>
   <si>
+    <t>Real Time - Intense Impression For Men - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350361</t>
   </si>
   <si>
+    <t>Real Time Canyon night 100 ml eau de toilette spray</t>
+  </si>
+  <si>
     <t>8715658002796</t>
   </si>
   <si>
+    <t>Sentio Inter Feer men Eau de toilette spray for him 100ml</t>
+  </si>
+  <si>
     <t>7640158815021</t>
   </si>
   <si>
+    <t>Omerta - Laverder Fields - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380702</t>
   </si>
   <si>
+    <t>Real Time Silenzia For Men - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
+    <t>8715658009054</t>
+  </si>
+  <si>
+    <t>Vibezz Blissful Life parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
     <t>7640158819180</t>
   </si>
   <si>
+    <t>Omerta Hatch Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658997702</t>
   </si>
   <si>
+    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658350705</t>
   </si>
   <si>
+    <t>Omerta - Invasion Third Dimension - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380368</t>
   </si>
   <si>
+    <t>Omerta - Faktz Select - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658370215</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Warm Wishes! And Cozy Kisses - Body Mist 250ml</t>
+  </si>
+  <si>
     <t>8721055492603</t>
   </si>
   <si>
+    <t>Real Time - Queen Of Space Glorious - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361473</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494225</t>
   </si>
   <si>
-    <t>946246</t>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Omerta - Sweet Pommy - Eau de parfum - 100ML</t>
   </si>
   <si>
     <t>8715658998563</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494263</t>
   </si>
   <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816691</t>
   </si>
   <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816653</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494270</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494232</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816714</t>
   </si>
   <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816615</t>
   </si>
   <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493211</t>
   </si>
   <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816790</t>
   </si>
   <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816837</t>
   </si>
   <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816813</t>
   </si>
   <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493198</t>
   </si>
   <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493228</t>
   </si>
   <si>
+    <t>Bubble Bliss Flamingo Giftbook Parfum You're Flamazing EDP voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055492207</t>
   </si>
   <si>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102706</t>
+  </si>
+  <si>
+    <t>Real Time Big Eagle Black Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658009573</t>
   </si>
   <si>
+    <t>NG - Phenom - Eau de Parfum 100ml voor dames</t>
+  </si>
+  <si>
     <t>8719214753641</t>
   </si>
   <si>
+    <t>NG Dominatio Woman Eau de Parfum - Damesparfum met frisse en elegante geur - 100ml</t>
+  </si>
+  <si>
     <t>7438235478494</t>
   </si>
   <si>
+    <t>Dorall Everscent Eau de Toilette voor dames - 100ml</t>
+  </si>
+  <si>
     <t>6291012875807</t>
   </si>
   <si>
+    <t>Savanna Nights - eau de toilette</t>
+  </si>
+  <si>
     <t>6291012871038</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Mermaid Pink - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055493464</t>
   </si>
   <si>
+    <t>Hello Kitty Mermaid Parfum set 6 stuks voor kinderen - 6x15ml - Meisjes</t>
+  </si>
+  <si>
     <t>8721055493105</t>
   </si>
   <si>
+    <t>Sentio Chalize for Woman giftset geuren 3x 15ml soorten eau de parfum</t>
+  </si>
+  <si>
     <t>8721055492146</t>
   </si>
   <si>
+    <t>Real Time Wild Action Eau de Toilette Spray 100ml</t>
+  </si>
+  <si>
     <t>8715658350224</t>
   </si>
   <si>
+    <t>Omerta Power Boost For Men Eau de Toilette Spray 100ml</t>
+  </si>
+  <si>
     <t>8715658370208</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Kisses - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055493440</t>
   </si>
   <si>
+    <t>Vibezz Il Capitano - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
     <t>7640158819241</t>
   </si>
   <si>
+    <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
+  </si>
+  <si>
     <t>6151010029070</t>
   </si>
   <si>
+    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380801</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Unicorn Cloud - Showergel + Water-Based Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>7640158816974</t>
   </si>
   <si>
+    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360995</t>
   </si>
   <si>
+    <t>Creation Lamis Diva Essence Eau de Parfum For Women 100ml</t>
+  </si>
+  <si>
     <t>6291012005662</t>
   </si>
   <si>
+    <t>Creation Lamis Fatal Snake Magical Giftset</t>
+  </si>
+  <si>
     <t>6291012871731</t>
   </si>
   <si>
+    <t>Sentio Spin Me Round Eau de Parfum For Her 50ml</t>
+  </si>
+  <si>
     <t>8721055491798</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Family Magical - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492740</t>
   </si>
   <si>
+    <t>Sentio I Love You Giftset</t>
+  </si>
+  <si>
     <t>8721055494126</t>
   </si>
   <si>
+    <t>Hello Kitty Club Eau de Parfum voor Kinderen 50 ml - You Go Girl!</t>
+  </si>
+  <si>
     <t>8721055493341</t>
   </si>
   <si>
+    <t>Creation Lamis My Spirit Eau de Parfum For Women 100ml</t>
+  </si>
+  <si>
     <t>6291012005648</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Merry Christmas And Happy New Year - Body Mist 250ml</t>
+  </si>
+  <si>
     <t>8721055495970</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Rainbow - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055493426</t>
   </si>
   <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
     <t>6291012005082</t>
   </si>
   <si>
+    <t>Dorall 24 pure for men eau de toilette herenparfum 100ml</t>
+  </si>
+  <si>
     <t>5414666010511</t>
   </si>
   <si>
+    <t>Bubble Bliss - Giftset - Unicorn Cherry Blossom Fantasy - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055494065</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Holly Jolly Magic - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492719</t>
   </si>
   <si>
+    <t>Sentio Twirl Once More Eau de Parfum For Her 50ml</t>
+  </si>
+  <si>
     <t>8721055491781</t>
   </si>
   <si>
+    <t>Sentio Soft Suede Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8721055491453</t>
   </si>
   <si>
+    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658340287</t>
   </si>
   <si>
+    <t>NG Touch! / Eau de parfum / 80 ml</t>
+  </si>
+  <si>
     <t>8718421831555</t>
   </si>
   <si>
+    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370574</t>
   </si>
   <si>
+    <t>Omerta - Express sensualite Captive - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658999027</t>
   </si>
   <si>
+    <t>Linn Young "Je Suis Sure Et Certaine" Eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658400295</t>
   </si>
   <si>
+    <t>Real Time - Please Call Me - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360971</t>
   </si>
   <si>
+    <t>Real Time Queen of Space parfum - Eau de parfum voor elegante vrouwen - 100ml</t>
+  </si>
+  <si>
     <t>8715658360896</t>
   </si>
   <si>
+    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350033</t>
   </si>
   <si>
+    <t>Real Time - Nuit Charmante - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360001</t>
   </si>
   <si>
+    <t>Bubble Bliss Blooming Bella Parfum Giftbag - Eau de parfum voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055494300</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Happy Holidays - Body Mist 250ml</t>
+  </si>
+  <si>
     <t>8721055493082</t>
   </si>
   <si>
+    <t>Next Generation Classic Woman Elegance Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214753269</t>
   </si>
   <si>
+    <t>Hello Kitty Graffiti parfum - Eau de parfum voor kinderen - 50 ml</t>
+  </si>
+  <si>
     <t>7640158816851</t>
   </si>
   <si>
+    <t>Vibezz-French Marine-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
     <t>7640158819234</t>
   </si>
   <si>
+    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
     <t>7640158819173</t>
   </si>
   <si>
+    <t>Street Looks - Pure Courage - Eau de Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658013082</t>
   </si>
   <si>
+    <t>Street Looks - La Creation Pour Femme - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658013020</t>
   </si>
   <si>
+    <t>Street Looks Uptown Babe eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658340270</t>
   </si>
   <si>
+    <t>Real Time - Morning Bloom - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361428</t>
   </si>
   <si>
+    <t>Real Time Cops For Men 2.0 - Eau de Toilette voor heren - 100ML</t>
+  </si>
+  <si>
     <t>8715658350620</t>
   </si>
   <si>
+    <t>Omerta -Meet Me Extreme- 100ml Eau de Toilette for men</t>
+  </si>
+  <si>
     <t>8715658370420</t>
   </si>
   <si>
+    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658997924</t>
   </si>
   <si>
+    <t>Real Time - Sea Beach - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658002840</t>
   </si>
   <si>
+    <t>Real Time - Queen Of Space Blazing Sky - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658360865</t>
   </si>
   <si>
+    <t>Street Looks - Amour Fatale - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658012948</t>
   </si>
   <si>
+    <t>Next Generation Touch Desire Eau de Parfum 80ml</t>
+  </si>
+  <si>
     <t>8719214752699</t>
   </si>
   <si>
+    <t>Real Time - Blooming Flower Nectar - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361435</t>
   </si>
   <si>
+    <t>Bubble Bliss Flamingo Giftbook Parfum Pink &amp; Proud EDP voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055492184</t>
   </si>
   <si>
+    <t>Vibezz-24K-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
     <t>7640158819265</t>
   </si>
   <si>
+    <t>Real Time - Call Me Black Edition - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350514</t>
   </si>
   <si>
+    <t>Omerta Omd Oh My Dear 100 ml - Eau De Parfum Spray Damesparfum</t>
+  </si>
+  <si>
     <t>8715658380030</t>
   </si>
   <si>
+    <t>Omerta Putting Green Eau de Toilette Pour Homme - 100ml</t>
+  </si>
+  <si>
     <t>8715658998952</t>
   </si>
   <si>
+    <t>Vibezz-Infusion Noir-Eau de Parfum For Her-100ml</t>
+  </si>
+  <si>
     <t>7640158819203</t>
   </si>
   <si>
+    <t>Omerta - Rose Pure - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380696</t>
   </si>
   <si>
+    <t>Omerta - Happy Love Fun For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380399</t>
   </si>
   <si>
+    <t>SENTIO FEESTDAGEN PINK - Enchanting Glow - Eau de Parfum 50ml</t>
+  </si>
+  <si>
     <t>8721055492726</t>
   </si>
   <si>
+    <t>Vibezz-Solitude-Eau de Toilette For Him-100ml</t>
+  </si>
+  <si>
     <t>7640158819258</t>
   </si>
   <si>
+    <t>Creation Lamis - Espy - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>5414666016452</t>
   </si>
   <si>
+    <t>Real Time - Yes Call Me - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360964</t>
   </si>
   <si>
+    <t>Omerta - Acqua Di Omerta - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370154</t>
   </si>
   <si>
+    <t>Omerta - Couture Cat - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658997733</t>
   </si>
   <si>
+    <t>Omerta - Out Of Question - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380412</t>
   </si>
   <si>
+    <t>Sentio Chalize Eau De Parfum - 100 ml</t>
+  </si>
+  <si>
     <t>7640158815694</t>
   </si>
   <si>
+    <t>Next Generation Classic for Woman 100ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8719214750961</t>
   </si>
   <si>
+    <t>NG Lightness Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214758363</t>
   </si>
   <si>
+    <t>NG Nightly Desire Eau de Toilette 100 ml</t>
+  </si>
+  <si>
     <t>8718421831913</t>
   </si>
   <si>
+    <t>Creation Lamis - Golden Wave - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>5414666011471</t>
   </si>
   <si>
+    <t>De La Mare Parfum Raggio Di Sole 36 Berry &amp; Amber Plum Eau de Parfum 100 ml</t>
+  </si>
+  <si>
     <t>8721055498131</t>
   </si>
   <si>
+    <t>Bubble Bliss Fantastic Flamingo - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
+  </si>
+  <si>
     <t>8721055493914</t>
   </si>
   <si>
+    <t>Hello Kitty - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
+  </si>
+  <si>
     <t>8721055493181</t>
   </si>
   <si>
+    <t>Real Time Love You Red 100 ml - Eau de Parfum - Damesparfum</t>
+  </si>
+  <si>
     <t>8715658360056</t>
   </si>
   <si>
+    <t>Hello Kitty Unicorn Parfum set 6 stuks voor kinderen - 6x15ml - Meisjes</t>
+  </si>
+  <si>
     <t>7640158816929</t>
   </si>
   <si>
+    <t>Bubble Bliss Like a Fairytale - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
+  </si>
+  <si>
     <t>8721055494218</t>
   </si>
   <si>
+    <t>Creation Lamis Golden Wave Women Giftset</t>
+  </si>
+  <si>
     <t>6291012002623</t>
   </si>
   <si>
+    <t>Bubble Bliss Parfum Giftbag Glimmering Grace EDP voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055494324</t>
   </si>
   <si>
+    <t>Creation Lamis Golden Wave for Men Giftset</t>
+  </si>
+  <si>
     <t>6291012002661</t>
   </si>
   <si>
+    <t>Real Time - Racing Horse Gold - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350255</t>
   </si>
   <si>
+    <t>Hello Kitty Delicate Flower Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
     <t>7640158816875</t>
   </si>
   <si>
+    <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360759</t>
   </si>
   <si>
+    <t>Omerta - Vanilla Fun - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658999447</t>
   </si>
   <si>
+    <t>De La Mare Parfum Raggio Di Sole 49 Caramel &amp; Pistachio Eau de Parfum 100 ml</t>
+  </si>
+  <si>
     <t>8721055498155</t>
   </si>
   <si>
+    <t>Street Looks - Oh La Chicca - Eau de parfum - 100 ml</t>
+  </si>
+  <si>
     <t>8715658013075</t>
   </si>
   <si>
+    <t>MEEKA Ouvert Eau de Parfum - Bloemige geur met lavendel en oranjebloesem - 100ml</t>
+  </si>
+  <si>
     <t>8719214754105</t>
+  </si>
+  <si>
+    <t>Real Time - Journee Joyeuse - Eau De Parfum - 100ML</t>
   </si>
   <si>
     <t>8715658360018</t>
@@ -876,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -920,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>24.95</v>
@@ -932,21 +1385,21 @@
         <v>0.52</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>24.43</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>9.94</v>
@@ -958,21 +1411,21 @@
         <v>0.46</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
         <v>9.48</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>15.19</v>
@@ -984,73 +1437,73 @@
         <v>0.39</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
         <v>14.8</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>13.95</v>
+        <v>9.79</v>
       </c>
       <c r="D5" s="1">
-        <v>13.62</v>
+        <v>9.45</v>
       </c>
       <c r="E5" s="1">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>13.62</v>
+        <v>9.45</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D6" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="E6" s="1">
         <v>0.33</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>14.59</v>
@@ -1062,73 +1515,73 @@
         <v>0.33</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>14.26</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D8" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="E8" s="1">
         <v>0.33</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D9" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="E9" s="1">
         <v>0.33</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>14.59</v>
@@ -1140,73 +1593,73 @@
         <v>0.33</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>14.26</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
-        <v>14.69</v>
+        <v>14.59</v>
       </c>
       <c r="D11" s="1">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="E11" s="1">
         <v>0.33</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
-        <v>14.59</v>
+        <v>14.69</v>
       </c>
       <c r="D12" s="1">
-        <v>14.26</v>
+        <v>14.36</v>
       </c>
       <c r="E12" s="1">
         <v>0.33</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>14.26</v>
+        <v>14.36</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>14.59</v>
@@ -1218,21 +1671,21 @@
         <v>0.33</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
         <v>14.26</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1">
         <v>14.59</v>
@@ -1244,21 +1697,21 @@
         <v>0.33</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
         <v>14.26</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1">
         <v>14.59</v>
@@ -1270,47 +1723,47 @@
         <v>0.33</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
         <v>14.26</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D16" s="1">
-        <v>13.68</v>
+        <v>14.26</v>
       </c>
       <c r="E16" s="1">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>13.68</v>
+        <v>14.26</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>13.95</v>
@@ -1322,21 +1775,21 @@
         <v>0.27</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
         <v>13.68</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1">
         <v>13.95</v>
@@ -1348,21 +1801,21 @@
         <v>0.27</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="1">
         <v>13.68</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1">
         <v>13.95</v>
@@ -1374,21 +1827,21 @@
         <v>0.27</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1">
         <v>13.68</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1">
         <v>13.95</v>
@@ -1400,21 +1853,21 @@
         <v>0.27</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="1">
         <v>13.68</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>13.95</v>
@@ -1426,21 +1879,21 @@
         <v>0.27</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" s="1">
         <v>13.68</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>13.95</v>
@@ -1452,21 +1905,21 @@
         <v>0.27</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
         <v>13.68</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
         <v>13.95</v>
@@ -1478,21 +1931,21 @@
         <v>0.27</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="1">
         <v>13.68</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1">
         <v>13.95</v>
@@ -1504,21 +1957,21 @@
         <v>0.27</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
         <v>13.68</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1">
         <v>13.95</v>
@@ -1530,21 +1983,21 @@
         <v>0.27</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="1">
         <v>13.68</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1">
         <v>13.95</v>
@@ -1556,21 +2009,21 @@
         <v>0.27</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="1">
         <v>13.68</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1">
         <v>13.95</v>
@@ -1582,21 +2035,21 @@
         <v>0.27</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
         <v>13.68</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1">
         <v>13.95</v>
@@ -1608,21 +2061,21 @@
         <v>0.27</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="1">
         <v>13.68</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1">
         <v>13.95</v>
@@ -1634,21 +2087,21 @@
         <v>0.27</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
         <v>13.68</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>13.95</v>
@@ -1660,125 +2113,125 @@
         <v>0.27</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
         <v>13.68</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1">
         <v>13.95</v>
       </c>
       <c r="D31" s="1">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="E31" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1">
-        <v>13.89</v>
+        <v>13.95</v>
       </c>
       <c r="D32" s="1">
-        <v>13.63</v>
+        <v>13.68</v>
       </c>
       <c r="E32" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>13.63</v>
+        <v>13.68</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D33" s="1">
-        <v>4.99</v>
+        <v>13.69</v>
       </c>
       <c r="E33" s="1">
         <v>0.26</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>4.99</v>
+        <v>13.69</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C34" s="1">
-        <v>12.95</v>
+        <v>13.89</v>
       </c>
       <c r="D34" s="1">
-        <v>12.69</v>
+        <v>13.63</v>
       </c>
       <c r="E34" s="1">
         <v>0.26</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>12.69</v>
+        <v>13.63</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>5.25</v>
@@ -1790,47 +2243,47 @@
         <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G35" s="1">
         <v>4.99</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
-        <v>5.25</v>
+        <v>12.95</v>
       </c>
       <c r="D36" s="1">
-        <v>4.99</v>
+        <v>12.69</v>
       </c>
       <c r="E36" s="1">
         <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>4.99</v>
+        <v>12.69</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>5.25</v>
@@ -1842,21 +2295,21 @@
         <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G37" s="1">
         <v>4.99</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>5.25</v>
@@ -1868,21 +2321,21 @@
         <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G38" s="1">
         <v>4.99</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>5.25</v>
@@ -1894,21 +2347,21 @@
         <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G39" s="1">
         <v>4.99</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>5.25</v>
@@ -1920,21 +2373,21 @@
         <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G40" s="1">
         <v>4.99</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>5.25</v>
@@ -1946,21 +2399,21 @@
         <v>0.26</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G41" s="1">
         <v>4.99</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>5.25</v>
@@ -1972,21 +2425,21 @@
         <v>0.26</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G42" s="1">
         <v>4.99</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>5.25</v>
@@ -1998,21 +2451,21 @@
         <v>0.26</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G43" s="1">
         <v>4.99</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>5.25</v>
@@ -2024,21 +2477,21 @@
         <v>0.26</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G44" s="1">
         <v>4.99</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>5.25</v>
@@ -2050,21 +2503,21 @@
         <v>0.26</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G45" s="1">
         <v>4.99</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1">
         <v>5.25</v>
@@ -2076,21 +2529,21 @@
         <v>0.26</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G46" s="1">
         <v>4.99</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1">
         <v>5.25</v>
@@ -2102,21 +2555,21 @@
         <v>0.26</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G47" s="1">
         <v>4.99</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1">
         <v>5.25</v>
@@ -2128,21 +2581,21 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G48" s="1">
         <v>4.99</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="C49" s="1">
         <v>5.25</v>
@@ -2154,437 +2607,437 @@
         <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G49" s="1">
         <v>4.99</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D50" s="1">
-        <v>13.7</v>
+        <v>4.99</v>
       </c>
       <c r="E50" s="1">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F50" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="G50" s="1">
-        <v>13.7</v>
+        <v>4.99</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1">
-        <v>12.15</v>
+        <v>5.25</v>
       </c>
       <c r="D51" s="1">
-        <v>11.91</v>
+        <v>4.99</v>
       </c>
       <c r="E51" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="G51" s="1">
-        <v>11.91</v>
+        <v>4.99</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1">
-        <v>12.5</v>
+        <v>13.95</v>
       </c>
       <c r="D52" s="1">
-        <v>12.26</v>
+        <v>13.7</v>
       </c>
       <c r="E52" s="1">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G52" s="1">
-        <v>12.26</v>
+        <v>13.7</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1">
-        <v>12.5</v>
+        <v>14.25</v>
       </c>
       <c r="D53" s="1">
-        <v>12.26</v>
+        <v>14.01</v>
       </c>
       <c r="E53" s="1">
         <v>0.24</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G53" s="1">
-        <v>12.26</v>
+        <v>14.01</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1">
-        <v>13.69</v>
+        <v>12.15</v>
       </c>
       <c r="D54" s="1">
-        <v>13.46</v>
+        <v>11.91</v>
       </c>
       <c r="E54" s="1">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G54" s="1">
-        <v>13.46</v>
+        <v>11.91</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1">
-        <v>13.55</v>
+        <v>12.5</v>
       </c>
       <c r="D55" s="1">
-        <v>13.33</v>
+        <v>12.26</v>
       </c>
       <c r="E55" s="1">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1">
-        <v>13.33</v>
+        <v>12.26</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C56" s="1">
-        <v>16.95</v>
+        <v>12.5</v>
       </c>
       <c r="D56" s="1">
-        <v>16.73</v>
+        <v>12.26</v>
       </c>
       <c r="E56" s="1">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G56" s="1">
-        <v>16.73</v>
+        <v>12.26</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="C57" s="1">
-        <v>21.99</v>
+        <v>13.69</v>
       </c>
       <c r="D57" s="1">
-        <v>21.77</v>
+        <v>13.46</v>
       </c>
       <c r="E57" s="1">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G57" s="1">
-        <v>21.77</v>
+        <v>13.46</v>
       </c>
       <c r="H57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="C58" s="1">
-        <v>15.25</v>
+        <v>13.55</v>
       </c>
       <c r="D58" s="1">
-        <v>15.05</v>
+        <v>13.33</v>
       </c>
       <c r="E58" s="1">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G58" s="1">
-        <v>15.05</v>
+        <v>13.33</v>
       </c>
       <c r="H58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="C59" s="1">
-        <v>13.25</v>
+        <v>16.95</v>
       </c>
       <c r="D59" s="1">
-        <v>13.06</v>
+        <v>16.73</v>
       </c>
       <c r="E59" s="1">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G59" s="1">
-        <v>13.06</v>
+        <v>16.73</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="C60" s="1">
-        <v>13.19</v>
+        <v>21.99</v>
       </c>
       <c r="D60" s="1">
-        <v>13</v>
+        <v>21.77</v>
       </c>
       <c r="E60" s="1">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60" s="1">
-        <v>13</v>
+        <v>21.77</v>
       </c>
       <c r="H60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="C61" s="1">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="D61" s="1">
-        <v>14.06</v>
+        <v>15.05</v>
       </c>
       <c r="E61" s="1">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G61" s="1">
-        <v>14.06</v>
+        <v>15.05</v>
       </c>
       <c r="H61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C62" s="1">
-        <v>13.99</v>
+        <v>13.25</v>
       </c>
       <c r="D62" s="1">
-        <v>13.82</v>
+        <v>13.06</v>
       </c>
       <c r="E62" s="1">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G62" s="1">
-        <v>13.82</v>
+        <v>13.06</v>
       </c>
       <c r="H62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="C63" s="1">
-        <v>13.95</v>
+        <v>13.19</v>
       </c>
       <c r="D63" s="1">
-        <v>13.78</v>
+        <v>13</v>
       </c>
       <c r="E63" s="1">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G63" s="1">
-        <v>13.78</v>
+        <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="C64" s="1">
-        <v>13.95</v>
+        <v>14.25</v>
       </c>
       <c r="D64" s="1">
-        <v>13.78</v>
+        <v>14.06</v>
       </c>
       <c r="E64" s="1">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F64" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G64" s="1">
-        <v>13.78</v>
+        <v>14.06</v>
       </c>
       <c r="H64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1">
-        <v>14.75</v>
+        <v>13.99</v>
       </c>
       <c r="D65" s="1">
-        <v>14.58</v>
+        <v>13.82</v>
       </c>
       <c r="E65" s="1">
         <v>0.17</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G65" s="1">
-        <v>14.58</v>
+        <v>13.82</v>
       </c>
       <c r="H65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="C66" s="1">
         <v>13.95</v>
@@ -2596,151 +3049,151 @@
         <v>0.17</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G66" s="1">
         <v>13.78</v>
       </c>
       <c r="H66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="C67" s="1">
-        <v>14.75</v>
+        <v>13.95</v>
       </c>
       <c r="D67" s="1">
-        <v>14.58</v>
+        <v>13.78</v>
       </c>
       <c r="E67" s="1">
         <v>0.17</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G67" s="1">
-        <v>14.58</v>
+        <v>13.78</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="C68" s="1">
-        <v>13.69</v>
+        <v>14.75</v>
       </c>
       <c r="D68" s="1">
-        <v>13.52</v>
+        <v>14.58</v>
       </c>
       <c r="E68" s="1">
         <v>0.17</v>
       </c>
       <c r="F68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>13.52</v>
+        <v>14.58</v>
       </c>
       <c r="H68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="C69" s="1">
         <v>13.95</v>
       </c>
       <c r="D69" s="1">
-        <v>13.79</v>
+        <v>13.78</v>
       </c>
       <c r="E69" s="1">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F69" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G69" s="1">
-        <v>13.79</v>
+        <v>13.78</v>
       </c>
       <c r="H69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C70" s="1">
-        <v>13.95</v>
+        <v>14.75</v>
       </c>
       <c r="D70" s="1">
-        <v>13.79</v>
+        <v>14.58</v>
       </c>
       <c r="E70" s="1">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F70" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G70" s="1">
-        <v>13.79</v>
+        <v>14.58</v>
       </c>
       <c r="H70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1">
-        <v>14.59</v>
+        <v>13.69</v>
       </c>
       <c r="D71" s="1">
-        <v>14.43</v>
+        <v>13.52</v>
       </c>
       <c r="E71" s="1">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F71" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1">
-        <v>14.43</v>
+        <v>13.52</v>
       </c>
       <c r="H71" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="C72" s="1">
         <v>13.95</v>
@@ -2752,99 +3205,99 @@
         <v>0.16</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1">
         <v>13.79</v>
       </c>
       <c r="H72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="C73" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D73" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="E73" s="1">
         <v>0.16</v>
       </c>
       <c r="F73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G73" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="H73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="C74" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D74" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="E74" s="1">
         <v>0.16</v>
       </c>
       <c r="F74" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G74" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="H74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="C75" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D75" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="E75" s="1">
         <v>0.16</v>
       </c>
       <c r="F75" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="H75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="C76" s="1">
         <v>14.59</v>
@@ -2856,47 +3309,47 @@
         <v>0.16</v>
       </c>
       <c r="F76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G76" s="1">
         <v>14.43</v>
       </c>
       <c r="H76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="C77" s="1">
-        <v>14.5</v>
+        <v>13.95</v>
       </c>
       <c r="D77" s="1">
-        <v>14.34</v>
+        <v>13.79</v>
       </c>
       <c r="E77" s="1">
         <v>0.16</v>
       </c>
       <c r="F77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G77" s="1">
-        <v>14.34</v>
+        <v>13.79</v>
       </c>
       <c r="H77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="C78" s="1">
         <v>14.59</v>
@@ -2908,73 +3361,73 @@
         <v>0.16</v>
       </c>
       <c r="F78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G78" s="1">
         <v>14.43</v>
       </c>
       <c r="H78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="C79" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D79" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="E79" s="1">
         <v>0.16</v>
       </c>
       <c r="F79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G79" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="H79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="C80" s="1">
-        <v>13.95</v>
+        <v>14.5</v>
       </c>
       <c r="D80" s="1">
-        <v>13.79</v>
+        <v>14.34</v>
       </c>
       <c r="E80" s="1">
         <v>0.16</v>
       </c>
       <c r="F80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G80" s="1">
-        <v>13.79</v>
+        <v>14.34</v>
       </c>
       <c r="H80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="C81" s="1">
         <v>14.59</v>
@@ -2986,203 +3439,203 @@
         <v>0.16</v>
       </c>
       <c r="F81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G81" s="1">
         <v>14.43</v>
       </c>
       <c r="H81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="C82" s="1">
-        <v>12.75</v>
+        <v>13.95</v>
       </c>
       <c r="D82" s="1">
-        <v>12.6</v>
+        <v>13.79</v>
       </c>
       <c r="E82" s="1">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G82" s="1">
-        <v>12.6</v>
+        <v>13.79</v>
       </c>
       <c r="H82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="C83" s="1">
-        <v>12.5</v>
+        <v>13.95</v>
       </c>
       <c r="D83" s="1">
-        <v>12.35</v>
+        <v>13.79</v>
       </c>
       <c r="E83" s="1">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G83" s="1">
-        <v>12.35</v>
+        <v>13.79</v>
       </c>
       <c r="H83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="C84" s="1">
-        <v>13.99</v>
+        <v>14.59</v>
       </c>
       <c r="D84" s="1">
-        <v>13.85</v>
+        <v>14.43</v>
       </c>
       <c r="E84" s="1">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G84" s="1">
-        <v>13.85</v>
+        <v>14.43</v>
       </c>
       <c r="H84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="C85" s="1">
-        <v>13.99</v>
+        <v>12.75</v>
       </c>
       <c r="D85" s="1">
-        <v>13.85</v>
+        <v>12.6</v>
       </c>
       <c r="E85" s="1">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>13.85</v>
+        <v>12.6</v>
       </c>
       <c r="H85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="C86" s="1">
-        <v>14.19</v>
+        <v>12.5</v>
       </c>
       <c r="D86" s="1">
-        <v>14.05</v>
+        <v>12.35</v>
       </c>
       <c r="E86" s="1">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F86" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G86" s="1">
-        <v>14.05</v>
+        <v>12.35</v>
       </c>
       <c r="H86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="C87" s="1">
-        <v>14.09</v>
+        <v>13.99</v>
       </c>
       <c r="D87" s="1">
-        <v>13.95</v>
+        <v>13.85</v>
       </c>
       <c r="E87" s="1">
         <v>0.14</v>
       </c>
       <c r="F87" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G87" s="1">
-        <v>13.95</v>
+        <v>13.85</v>
       </c>
       <c r="H87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="C88" s="1">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="D88" s="1">
-        <v>13.81</v>
+        <v>13.85</v>
       </c>
       <c r="E88" s="1">
         <v>0.14</v>
       </c>
       <c r="F88" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G88" s="1">
-        <v>13.81</v>
+        <v>13.85</v>
       </c>
       <c r="H88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="C89" s="1">
         <v>14.19</v>
@@ -3194,125 +3647,125 @@
         <v>0.14</v>
       </c>
       <c r="F89" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G89" s="1">
         <v>14.05</v>
       </c>
       <c r="H89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="C90" s="1">
-        <v>13.95</v>
+        <v>14.09</v>
       </c>
       <c r="D90" s="1">
-        <v>13.81</v>
+        <v>13.95</v>
       </c>
       <c r="E90" s="1">
         <v>0.14</v>
       </c>
       <c r="F90" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G90" s="1">
-        <v>13.81</v>
+        <v>13.95</v>
       </c>
       <c r="H90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="C91" s="1">
         <v>13.95</v>
       </c>
       <c r="D91" s="1">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="E91" s="1">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F91" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G91" s="1">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="H91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="C92" s="1">
-        <v>13.95</v>
+        <v>14.19</v>
       </c>
       <c r="D92" s="1">
-        <v>13.82</v>
+        <v>14.05</v>
       </c>
       <c r="E92" s="1">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G92" s="1">
-        <v>13.82</v>
+        <v>14.05</v>
       </c>
       <c r="H92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="B93" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="C93" s="1">
-        <v>12.5</v>
+        <v>13.95</v>
       </c>
       <c r="D93" s="1">
-        <v>12.37</v>
+        <v>13.81</v>
       </c>
       <c r="E93" s="1">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G93" s="1">
-        <v>12.37</v>
+        <v>13.81</v>
       </c>
       <c r="H93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="C94" s="1">
         <v>13.95</v>
@@ -3324,73 +3777,73 @@
         <v>0.13</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G94" s="1">
         <v>13.82</v>
       </c>
       <c r="H94" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="C95" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D95" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="E95" s="1">
         <v>0.13</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G95" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="H95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="C96" s="1">
-        <v>13.95</v>
+        <v>12.5</v>
       </c>
       <c r="D96" s="1">
-        <v>13.82</v>
+        <v>12.37</v>
       </c>
       <c r="E96" s="1">
         <v>0.13</v>
       </c>
       <c r="F96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G96" s="1">
-        <v>13.82</v>
+        <v>12.37</v>
       </c>
       <c r="H96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="C97" s="1">
         <v>13.95</v>
@@ -3402,73 +3855,73 @@
         <v>0.13</v>
       </c>
       <c r="F97" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G97" s="1">
         <v>13.82</v>
       </c>
       <c r="H97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="C98" s="1">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="D98" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="E98" s="1">
         <v>0.13</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G98" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="H98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="C99" s="1">
-        <v>13.1</v>
+        <v>13.95</v>
       </c>
       <c r="D99" s="1">
-        <v>12.97</v>
+        <v>13.82</v>
       </c>
       <c r="E99" s="1">
         <v>0.13</v>
       </c>
       <c r="F99" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G99" s="1">
-        <v>12.97</v>
+        <v>13.82</v>
       </c>
       <c r="H99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="C100" s="1">
         <v>13.95</v>
@@ -3480,21 +3933,21 @@
         <v>0.13</v>
       </c>
       <c r="F100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G100" s="1">
         <v>13.82</v>
       </c>
       <c r="H100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="C101" s="1">
         <v>13.95</v>
@@ -3506,47 +3959,47 @@
         <v>0.13</v>
       </c>
       <c r="F101" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G101" s="1">
         <v>13.82</v>
       </c>
       <c r="H101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="C102" s="1">
-        <v>13.95</v>
+        <v>13.1</v>
       </c>
       <c r="D102" s="1">
-        <v>13.82</v>
+        <v>12.97</v>
       </c>
       <c r="E102" s="1">
         <v>0.13</v>
       </c>
       <c r="F102" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G102" s="1">
-        <v>13.82</v>
+        <v>12.97</v>
       </c>
       <c r="H102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>215</v>
       </c>
       <c r="B103" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="C103" s="1">
         <v>13.95</v>
@@ -3558,21 +4011,21 @@
         <v>0.13</v>
       </c>
       <c r="F103" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G103" s="1">
         <v>13.82</v>
       </c>
       <c r="H103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="C104" s="1">
         <v>13.95</v>
@@ -3584,21 +4037,21 @@
         <v>0.13</v>
       </c>
       <c r="F104" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
         <v>13.82</v>
       </c>
       <c r="H104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="C105" s="1">
         <v>13.95</v>
@@ -3610,21 +4063,21 @@
         <v>0.13</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G105" s="1">
         <v>13.82</v>
       </c>
       <c r="H105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="C106" s="1">
         <v>13.95</v>
@@ -3636,21 +4089,21 @@
         <v>0.13</v>
       </c>
       <c r="F106" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G106" s="1">
         <v>13.82</v>
       </c>
       <c r="H106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="C107" s="1">
         <v>13.95</v>
@@ -3662,21 +4115,21 @@
         <v>0.13</v>
       </c>
       <c r="F107" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G107" s="1">
         <v>13.82</v>
       </c>
       <c r="H107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>118</v>
+        <v>225</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="C108" s="1">
         <v>13.95</v>
@@ -3688,21 +4141,21 @@
         <v>0.13</v>
       </c>
       <c r="F108" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G108" s="1">
         <v>13.82</v>
       </c>
       <c r="H108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="B109" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="C109" s="1">
         <v>13.95</v>
@@ -3714,21 +4167,21 @@
         <v>0.13</v>
       </c>
       <c r="F109" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G109" s="1">
         <v>13.82</v>
       </c>
       <c r="H109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="C110" s="1">
         <v>13.95</v>
@@ -3740,21 +4193,21 @@
         <v>0.13</v>
       </c>
       <c r="F110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G110" s="1">
         <v>13.82</v>
       </c>
       <c r="H110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>232</v>
       </c>
       <c r="C111" s="1">
         <v>13.95</v>
@@ -3766,21 +4219,21 @@
         <v>0.13</v>
       </c>
       <c r="F111" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G111" s="1">
         <v>13.82</v>
       </c>
       <c r="H111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="B112" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="C112" s="1">
         <v>13.95</v>
@@ -3792,47 +4245,47 @@
         <v>0.13</v>
       </c>
       <c r="F112" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G112" s="1">
         <v>13.82</v>
       </c>
       <c r="H112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="C113" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D113" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="E113" s="1">
         <v>0.13</v>
       </c>
       <c r="F113" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G113" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="H113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>238</v>
       </c>
       <c r="C114" s="1">
         <v>13.95</v>
@@ -3844,21 +4297,21 @@
         <v>0.13</v>
       </c>
       <c r="F114" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G114" s="1">
         <v>13.82</v>
       </c>
       <c r="H114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>125</v>
+        <v>239</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C115" s="1">
         <v>13.95</v>
@@ -3870,47 +4323,47 @@
         <v>0.13</v>
       </c>
       <c r="F115" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G115" s="1">
         <v>13.82</v>
       </c>
       <c r="H115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>126</v>
+        <v>241</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>242</v>
       </c>
       <c r="C116" s="1">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="D116" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="E116" s="1">
         <v>0.13</v>
       </c>
       <c r="F116" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G116" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="H116" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="C117" s="1">
         <v>13.95</v>
@@ -3922,21 +4375,21 @@
         <v>0.13</v>
       </c>
       <c r="F117" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G117" s="1">
         <v>13.82</v>
       </c>
       <c r="H117" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>246</v>
       </c>
       <c r="C118" s="1">
         <v>13.95</v>
@@ -3948,21 +4401,21 @@
         <v>0.13</v>
       </c>
       <c r="F118" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G118" s="1">
         <v>13.82</v>
       </c>
       <c r="H118" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>129</v>
+        <v>247</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="C119" s="1">
         <v>13.95</v>
@@ -3974,21 +4427,21 @@
         <v>0.13</v>
       </c>
       <c r="F119" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G119" s="1">
         <v>13.82</v>
       </c>
       <c r="H119" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>249</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="C120" s="1">
         <v>13.95</v>
@@ -4000,47 +4453,47 @@
         <v>0.13</v>
       </c>
       <c r="F120" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G120" s="1">
         <v>13.82</v>
       </c>
       <c r="H120" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="C121" s="1">
-        <v>14.09</v>
+        <v>13.95</v>
       </c>
       <c r="D121" s="1">
-        <v>13.96</v>
+        <v>13.82</v>
       </c>
       <c r="E121" s="1">
         <v>0.13</v>
       </c>
       <c r="F121" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G121" s="1">
-        <v>13.96</v>
+        <v>13.82</v>
       </c>
       <c r="H121" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="C122" s="1">
         <v>13.95</v>
@@ -4052,125 +4505,125 @@
         <v>0.13</v>
       </c>
       <c r="F122" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G122" s="1">
         <v>13.82</v>
       </c>
       <c r="H122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>256</v>
       </c>
       <c r="C123" s="1">
-        <v>13.89</v>
+        <v>13.95</v>
       </c>
       <c r="D123" s="1">
-        <v>13.76</v>
+        <v>13.82</v>
       </c>
       <c r="E123" s="1">
         <v>0.13</v>
       </c>
       <c r="F123" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G123" s="1">
-        <v>13.76</v>
+        <v>13.82</v>
       </c>
       <c r="H123" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="C124" s="1">
-        <v>12.45</v>
+        <v>14.09</v>
       </c>
       <c r="D124" s="1">
-        <v>12.33</v>
+        <v>13.96</v>
       </c>
       <c r="E124" s="1">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F124" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G124" s="1">
-        <v>12.33</v>
+        <v>13.96</v>
       </c>
       <c r="H124" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="C125" s="1">
-        <v>12.5</v>
+        <v>13.95</v>
       </c>
       <c r="D125" s="1">
-        <v>12.38</v>
+        <v>13.82</v>
       </c>
       <c r="E125" s="1">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F125" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G125" s="1">
-        <v>12.38</v>
+        <v>13.82</v>
       </c>
       <c r="H125" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="C126" s="1">
-        <v>12.5</v>
+        <v>13.89</v>
       </c>
       <c r="D126" s="1">
-        <v>12.38</v>
+        <v>13.76</v>
       </c>
       <c r="E126" s="1">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F126" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G126" s="1">
-        <v>12.38</v>
+        <v>13.76</v>
       </c>
       <c r="H126" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="C127" s="1">
         <v>12.45</v>
@@ -4182,507 +4635,585 @@
         <v>0.12</v>
       </c>
       <c r="F127" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G127" s="1">
         <v>12.33</v>
       </c>
       <c r="H127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>138</v>
+        <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="C128" s="1">
-        <v>13.59</v>
+        <v>12.5</v>
       </c>
       <c r="D128" s="1">
-        <v>13.47</v>
+        <v>12.38</v>
       </c>
       <c r="E128" s="1">
         <v>0.12</v>
       </c>
       <c r="F128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G128" s="1">
-        <v>13.47</v>
+        <v>12.38</v>
       </c>
       <c r="H128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="C129" s="1">
-        <v>14.95</v>
+        <v>12.5</v>
       </c>
       <c r="D129" s="1">
-        <v>14.84</v>
+        <v>12.38</v>
       </c>
       <c r="E129" s="1">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F129" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G129" s="1">
-        <v>14.84</v>
+        <v>12.38</v>
       </c>
       <c r="H129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>140</v>
+        <v>269</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="C130" s="1">
-        <v>21.99</v>
+        <v>12.45</v>
       </c>
       <c r="D130" s="1">
-        <v>21.88</v>
+        <v>12.33</v>
       </c>
       <c r="E130" s="1">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F130" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G130" s="1">
-        <v>21.88</v>
+        <v>12.33</v>
       </c>
       <c r="H130" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>141</v>
+        <v>271</v>
       </c>
       <c r="B131" t="s">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="C131" s="1">
-        <v>21.99</v>
+        <v>13.59</v>
       </c>
       <c r="D131" s="1">
-        <v>21.88</v>
+        <v>13.47</v>
       </c>
       <c r="E131" s="1">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F131" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G131" s="1">
-        <v>21.88</v>
+        <v>13.47</v>
       </c>
       <c r="H131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="C132" s="1">
-        <v>13.25</v>
+        <v>14.95</v>
       </c>
       <c r="D132" s="1">
-        <v>13.15</v>
+        <v>14.84</v>
       </c>
       <c r="E132" s="1">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F132" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G132" s="1">
-        <v>13.15</v>
+        <v>14.84</v>
       </c>
       <c r="H132" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="C133" s="1">
         <v>21.99</v>
       </c>
       <c r="D133" s="1">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="E133" s="1">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F133" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G133" s="1">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="H133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>144</v>
+        <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="C134" s="1">
         <v>21.99</v>
       </c>
       <c r="D134" s="1">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="E134" s="1">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F134" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G134" s="1">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="H134" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>280</v>
       </c>
       <c r="C135" s="1">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="D135" s="1">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="E135" s="1">
         <v>0.1</v>
       </c>
       <c r="F135" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G135" s="1">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="H135" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>146</v>
+        <v>281</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="C136" s="1">
-        <v>13.29</v>
+        <v>21.99</v>
       </c>
       <c r="D136" s="1">
-        <v>13.2</v>
+        <v>21.89</v>
       </c>
       <c r="E136" s="1">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F136" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G136" s="1">
-        <v>13.2</v>
+        <v>21.89</v>
       </c>
       <c r="H136" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>147</v>
+        <v>283</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>284</v>
       </c>
       <c r="C137" s="1">
-        <v>12.69</v>
+        <v>21.99</v>
       </c>
       <c r="D137" s="1">
-        <v>12.6</v>
+        <v>21.89</v>
       </c>
       <c r="E137" s="1">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G137" s="1">
-        <v>12.6</v>
+        <v>21.89</v>
       </c>
       <c r="H137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>148</v>
+        <v>285</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
       <c r="C138" s="1">
-        <v>12.99</v>
+        <v>13.43</v>
       </c>
       <c r="D138" s="1">
-        <v>12.91</v>
+        <v>13.33</v>
       </c>
       <c r="E138" s="1">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="F138" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G138" s="1">
-        <v>12.91</v>
+        <v>13.33</v>
       </c>
       <c r="H138" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>149</v>
+        <v>287</v>
       </c>
       <c r="B139" t="s">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="C139" s="1">
-        <v>12.95</v>
+        <v>13.29</v>
       </c>
       <c r="D139" s="1">
-        <v>12.87</v>
+        <v>13.2</v>
       </c>
       <c r="E139" s="1">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F139" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G139" s="1">
-        <v>12.87</v>
+        <v>13.2</v>
       </c>
       <c r="H139" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>150</v>
+        <v>289</v>
       </c>
       <c r="B140" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="C140" s="1">
-        <v>12.45</v>
+        <v>12.69</v>
       </c>
       <c r="D140" s="1">
-        <v>12.39</v>
+        <v>12.6</v>
       </c>
       <c r="E140" s="1">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="F140" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G140" s="1">
-        <v>12.39</v>
+        <v>12.6</v>
       </c>
       <c r="H140" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>151</v>
+        <v>291</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>292</v>
       </c>
       <c r="C141" s="1">
-        <v>14.59</v>
+        <v>12.99</v>
       </c>
       <c r="D141" s="1">
-        <v>14.54</v>
+        <v>12.91</v>
       </c>
       <c r="E141" s="1">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F141" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G141" s="1">
-        <v>14.54</v>
+        <v>12.91</v>
       </c>
       <c r="H141" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>294</v>
       </c>
       <c r="C142" s="1">
-        <v>14.95</v>
+        <v>12.95</v>
       </c>
       <c r="D142" s="1">
-        <v>14.9</v>
+        <v>12.87</v>
       </c>
       <c r="E142" s="1">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F142" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G142" s="1">
-        <v>14.9</v>
+        <v>12.87</v>
       </c>
       <c r="H142" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>153</v>
+        <v>295</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>296</v>
       </c>
       <c r="C143" s="1">
-        <v>11.59</v>
+        <v>12.45</v>
       </c>
       <c r="D143" s="1">
-        <v>11.54</v>
+        <v>12.39</v>
       </c>
       <c r="E143" s="1">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F143" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G143" s="1">
-        <v>11.54</v>
+        <v>12.39</v>
       </c>
       <c r="H143" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>298</v>
       </c>
       <c r="C144" s="1">
-        <v>11.59</v>
+        <v>14.59</v>
       </c>
       <c r="D144" s="1">
-        <v>11.54</v>
+        <v>14.54</v>
       </c>
       <c r="E144" s="1">
         <v>0.05</v>
       </c>
       <c r="F144" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G144" s="1">
-        <v>11.54</v>
+        <v>14.54</v>
       </c>
       <c r="H144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>155</v>
+        <v>299</v>
       </c>
       <c r="B145" t="s">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="C145" s="1">
-        <v>11.55</v>
+        <v>14.95</v>
       </c>
       <c r="D145" s="1">
-        <v>11.5</v>
+        <v>14.9</v>
       </c>
       <c r="E145" s="1">
         <v>0.05</v>
       </c>
       <c r="F145" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G145" s="1">
-        <v>11.5</v>
+        <v>14.9</v>
       </c>
       <c r="H145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>301</v>
       </c>
       <c r="B146" t="s">
-        <v>157</v>
+        <v>302</v>
       </c>
       <c r="C146" s="1">
+        <v>11.59</v>
+      </c>
+      <c r="D146" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F146" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="H146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>303</v>
+      </c>
+      <c r="B147" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="1">
+        <v>11.59</v>
+      </c>
+      <c r="D147" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F147" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="H147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>305</v>
+      </c>
+      <c r="B148" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="1">
+        <v>11.55</v>
+      </c>
+      <c r="D148" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="E148" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F148" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="H148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>307</v>
+      </c>
+      <c r="B149" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" s="1">
         <v>19.99</v>
       </c>
-      <c r="D146" s="1">
+      <c r="D149" s="1">
         <v>19.95</v>
       </c>
-      <c r="E146" s="1">
+      <c r="E149" s="1">
         <v>0.04</v>
       </c>
-      <c r="F146" t="s">
-        <v>9</v>
-      </c>
-      <c r="G146" s="1">
+      <c r="F149" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="1">
         <v>19.95</v>
       </c>
-      <c r="H146" t="s">
-        <v>10</v>
+      <c r="H149" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/prijsrapport-NL-2026-05-16.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="304">
   <si>
     <t>Product</t>
   </si>
@@ -37,42 +37,27 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>Creation Lamis Catsuit Man - Topparfum voor de zelfverzekerde man - 3 stuks</t>
-  </si>
-  <si>
-    <t>8719326174709</t>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>FBR</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>7640158817018</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>FBR</t>
-  </si>
-  <si>
-    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
-  </si>
-  <si>
-    <t>5414666014427</t>
-  </si>
-  <si>
-    <t>Juwelium</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158817018</t>
-  </si>
-  <si>
-    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>6291012000261</t>
-  </si>
-  <si>
-    <t>Dorsh</t>
-  </si>
-  <si>
     <t>SENTIO FEESTDAGEN PINK - Wonderful - Eau de Parfum 50ml</t>
   </si>
   <si>
@@ -358,12 +343,6 @@
     <t>8721055492207</t>
   </si>
   <si>
-    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
-  </si>
-  <si>
-    <t>8721349102706</t>
-  </si>
-  <si>
     <t>Real Time Big Eagle Black Eau de Toilette 100ml</t>
   </si>
   <si>
@@ -896,6 +875,12 @@
   </si>
   <si>
     <t>7640158816875</t>
+  </si>
+  <si>
+    <t>Sentio Love &amp; Casual for Him Eau de Toilette Spray 100 ml</t>
+  </si>
+  <si>
+    <t>8721055493723</t>
   </si>
   <si>
     <t>Real Time Loveliness La Passione - Eau de parfum - 100ML</t>
@@ -1329,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1376,19 +1361,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>24.95</v>
+        <v>9.94</v>
       </c>
       <c r="D2" s="1">
-        <v>24.43</v>
+        <v>9.48</v>
       </c>
       <c r="E2" s="1">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>24.43</v>
+        <v>9.48</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -1402,19 +1387,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>9.94</v>
+        <v>15.19</v>
       </c>
       <c r="D3" s="1">
-        <v>9.48</v>
+        <v>14.8</v>
       </c>
       <c r="E3" s="1">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>9.48</v>
+        <v>14.8</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1428,19 +1413,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>15.19</v>
+        <v>13.95</v>
       </c>
       <c r="D4" s="1">
-        <v>14.8</v>
+        <v>13.62</v>
       </c>
       <c r="E4" s="1">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>14.8</v>
+        <v>13.62</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1454,19 +1439,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>9.79</v>
+        <v>14.59</v>
       </c>
       <c r="D5" s="1">
-        <v>9.45</v>
+        <v>14.26</v>
       </c>
       <c r="E5" s="1">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>9.45</v>
+        <v>14.26</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -1474,25 +1459,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D6" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="E6" s="1">
         <v>0.33</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -1500,25 +1485,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D7" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="E7" s="1">
         <v>0.33</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>14.26</v>
+        <v>13.62</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -1526,10 +1511,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>14.59</v>
@@ -1541,7 +1526,7 @@
         <v>0.33</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
         <v>14.26</v>
@@ -1552,25 +1537,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D9" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="E9" s="1">
         <v>0.33</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
-        <v>13.62</v>
+        <v>14.26</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1578,25 +1563,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
       <c r="C10" s="1">
-        <v>14.59</v>
+        <v>14.69</v>
       </c>
       <c r="D10" s="1">
-        <v>14.26</v>
+        <v>14.36</v>
       </c>
       <c r="E10" s="1">
         <v>0.33</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
-        <v>14.26</v>
+        <v>14.36</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1604,10 +1589,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1">
         <v>14.59</v>
@@ -1619,7 +1604,7 @@
         <v>0.33</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
         <v>14.26</v>
@@ -1630,25 +1615,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="1">
-        <v>14.69</v>
+        <v>14.59</v>
       </c>
       <c r="D12" s="1">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="E12" s="1">
         <v>0.33</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1656,10 +1641,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>14.59</v>
@@ -1671,7 +1656,7 @@
         <v>0.33</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
         <v>14.26</v>
@@ -1682,10 +1667,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1">
         <v>14.59</v>
@@ -1697,7 +1682,7 @@
         <v>0.33</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
         <v>14.26</v>
@@ -1708,25 +1693,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D15" s="1">
-        <v>14.26</v>
+        <v>13.68</v>
       </c>
       <c r="E15" s="1">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
-        <v>14.26</v>
+        <v>13.68</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1734,25 +1719,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D16" s="1">
-        <v>14.26</v>
+        <v>13.68</v>
       </c>
       <c r="E16" s="1">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>14.26</v>
+        <v>13.68</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1760,10 +1745,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>13.95</v>
@@ -1775,7 +1760,7 @@
         <v>0.27</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
         <v>13.68</v>
@@ -1786,10 +1771,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
         <v>44</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
       </c>
       <c r="C18" s="1">
         <v>13.95</v>
@@ -1801,7 +1786,7 @@
         <v>0.27</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
         <v>13.68</v>
@@ -1812,10 +1797,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
       </c>
       <c r="C19" s="1">
         <v>13.95</v>
@@ -1827,7 +1812,7 @@
         <v>0.27</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
         <v>13.68</v>
@@ -1838,10 +1823,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
       </c>
       <c r="C20" s="1">
         <v>13.95</v>
@@ -1853,7 +1838,7 @@
         <v>0.27</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
         <v>13.68</v>
@@ -1864,10 +1849,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
         <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>13.95</v>
@@ -1879,7 +1864,7 @@
         <v>0.27</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
         <v>13.68</v>
@@ -1890,10 +1875,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
         <v>52</v>
-      </c>
-      <c r="B22" t="s">
-        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>13.95</v>
@@ -1905,7 +1890,7 @@
         <v>0.27</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1">
         <v>13.68</v>
@@ -1916,10 +1901,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
         <v>54</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
       </c>
       <c r="C23" s="1">
         <v>13.95</v>
@@ -1931,7 +1916,7 @@
         <v>0.27</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1">
         <v>13.68</v>
@@ -1942,10 +1927,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
         <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
       </c>
       <c r="C24" s="1">
         <v>13.95</v>
@@ -1957,7 +1942,7 @@
         <v>0.27</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1">
         <v>13.68</v>
@@ -1968,10 +1953,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
         <v>58</v>
-      </c>
-      <c r="B25" t="s">
-        <v>59</v>
       </c>
       <c r="C25" s="1">
         <v>13.95</v>
@@ -1983,7 +1968,7 @@
         <v>0.27</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25" s="1">
         <v>13.68</v>
@@ -1994,10 +1979,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
       </c>
       <c r="C26" s="1">
         <v>13.95</v>
@@ -2009,7 +1994,7 @@
         <v>0.27</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1">
         <v>13.68</v>
@@ -2020,10 +2005,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
       </c>
       <c r="C27" s="1">
         <v>13.95</v>
@@ -2035,7 +2020,7 @@
         <v>0.27</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G27" s="1">
         <v>13.68</v>
@@ -2046,10 +2031,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
         <v>64</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
       </c>
       <c r="C28" s="1">
         <v>13.95</v>
@@ -2061,7 +2046,7 @@
         <v>0.27</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
         <v>13.68</v>
@@ -2072,10 +2057,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
         <v>66</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
       </c>
       <c r="C29" s="1">
         <v>13.95</v>
@@ -2087,7 +2072,7 @@
         <v>0.27</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1">
         <v>13.68</v>
@@ -2098,10 +2083,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" t="s">
         <v>68</v>
-      </c>
-      <c r="B30" t="s">
-        <v>69</v>
       </c>
       <c r="C30" s="1">
         <v>13.95</v>
@@ -2113,7 +2098,7 @@
         <v>0.27</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1">
         <v>13.68</v>
@@ -2124,25 +2109,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
         <v>70</v>
       </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
       <c r="C31" s="1">
         <v>13.95</v>
       </c>
       <c r="D31" s="1">
-        <v>13.68</v>
+        <v>13.69</v>
       </c>
       <c r="E31" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G31" s="1">
-        <v>13.68</v>
+        <v>13.69</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -2150,25 +2135,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
       <c r="C32" s="1">
-        <v>13.95</v>
+        <v>13.89</v>
       </c>
       <c r="D32" s="1">
-        <v>13.68</v>
+        <v>13.63</v>
       </c>
       <c r="E32" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G32" s="1">
-        <v>13.68</v>
+        <v>13.63</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -2176,25 +2161,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
       <c r="C33" s="1">
-        <v>13.95</v>
+        <v>5.25</v>
       </c>
       <c r="D33" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="E33" s="1">
         <v>0.26</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G33" s="1">
-        <v>13.69</v>
+        <v>4.99</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -2208,19 +2193,19 @@
         <v>77</v>
       </c>
       <c r="C34" s="1">
-        <v>13.89</v>
+        <v>12.95</v>
       </c>
       <c r="D34" s="1">
-        <v>13.63</v>
+        <v>12.69</v>
       </c>
       <c r="E34" s="1">
         <v>0.26</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>13.63</v>
+        <v>12.69</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -2243,7 +2228,7 @@
         <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" s="1">
         <v>4.99</v>
@@ -2254,25 +2239,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
         <v>81</v>
       </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
       <c r="C36" s="1">
-        <v>12.95</v>
+        <v>5.25</v>
       </c>
       <c r="D36" s="1">
-        <v>12.69</v>
+        <v>4.99</v>
       </c>
       <c r="E36" s="1">
         <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G36" s="1">
-        <v>12.69</v>
+        <v>4.99</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2280,10 +2265,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
         <v>83</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>5.25</v>
@@ -2295,7 +2280,7 @@
         <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" s="1">
         <v>4.99</v>
@@ -2306,10 +2291,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>5.25</v>
@@ -2321,7 +2306,7 @@
         <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" s="1">
         <v>4.99</v>
@@ -2332,10 +2317,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>5.25</v>
@@ -2347,7 +2332,7 @@
         <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G39" s="1">
         <v>4.99</v>
@@ -2358,10 +2343,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
         <v>89</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>5.25</v>
@@ -2373,7 +2358,7 @@
         <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" s="1">
         <v>4.99</v>
@@ -2384,10 +2369,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
         <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>5.25</v>
@@ -2399,7 +2384,7 @@
         <v>0.26</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" s="1">
         <v>4.99</v>
@@ -2410,10 +2395,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
         <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>5.25</v>
@@ -2425,7 +2410,7 @@
         <v>0.26</v>
       </c>
       <c r="F42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" s="1">
         <v>4.99</v>
@@ -2436,10 +2421,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
         <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>5.25</v>
@@ -2451,7 +2436,7 @@
         <v>0.26</v>
       </c>
       <c r="F43" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" s="1">
         <v>4.99</v>
@@ -2462,10 +2447,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
         <v>97</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>5.25</v>
@@ -2477,7 +2462,7 @@
         <v>0.26</v>
       </c>
       <c r="F44" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" s="1">
         <v>4.99</v>
@@ -2488,10 +2473,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
         <v>99</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>5.25</v>
@@ -2503,7 +2488,7 @@
         <v>0.26</v>
       </c>
       <c r="F45" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G45" s="1">
         <v>4.99</v>
@@ -2514,10 +2499,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
         <v>101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>102</v>
       </c>
       <c r="C46" s="1">
         <v>5.25</v>
@@ -2529,7 +2514,7 @@
         <v>0.26</v>
       </c>
       <c r="F46" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" s="1">
         <v>4.99</v>
@@ -2540,10 +2525,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
         <v>103</v>
-      </c>
-      <c r="B47" t="s">
-        <v>104</v>
       </c>
       <c r="C47" s="1">
         <v>5.25</v>
@@ -2555,7 +2540,7 @@
         <v>0.26</v>
       </c>
       <c r="F47" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G47" s="1">
         <v>4.99</v>
@@ -2566,10 +2551,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
         <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
       </c>
       <c r="C48" s="1">
         <v>5.25</v>
@@ -2581,7 +2566,7 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G48" s="1">
         <v>4.99</v>
@@ -2592,10 +2577,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" t="s">
         <v>107</v>
-      </c>
-      <c r="B49" t="s">
-        <v>108</v>
       </c>
       <c r="C49" s="1">
         <v>5.25</v>
@@ -2607,7 +2592,7 @@
         <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G49" s="1">
         <v>4.99</v>
@@ -2618,25 +2603,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
         <v>109</v>
       </c>
-      <c r="B50" t="s">
-        <v>110</v>
-      </c>
       <c r="C50" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D50" s="1">
-        <v>4.99</v>
+        <v>13.7</v>
       </c>
       <c r="E50" s="1">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="F50" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="G50" s="1">
-        <v>4.99</v>
+        <v>13.7</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2644,25 +2629,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
       <c r="C51" s="1">
-        <v>5.25</v>
+        <v>12.15</v>
       </c>
       <c r="D51" s="1">
-        <v>4.99</v>
+        <v>11.91</v>
       </c>
       <c r="E51" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F51" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="G51" s="1">
-        <v>4.99</v>
+        <v>11.91</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2670,25 +2655,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
         <v>113</v>
       </c>
-      <c r="B52" t="s">
-        <v>114</v>
-      </c>
       <c r="C52" s="1">
-        <v>13.95</v>
+        <v>12.5</v>
       </c>
       <c r="D52" s="1">
-        <v>13.7</v>
+        <v>12.26</v>
       </c>
       <c r="E52" s="1">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G52" s="1">
-        <v>13.7</v>
+        <v>12.26</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2696,25 +2681,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
         <v>115</v>
       </c>
-      <c r="B53" t="s">
-        <v>116</v>
-      </c>
       <c r="C53" s="1">
-        <v>14.25</v>
+        <v>12.5</v>
       </c>
       <c r="D53" s="1">
-        <v>14.01</v>
+        <v>12.26</v>
       </c>
       <c r="E53" s="1">
         <v>0.24</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G53" s="1">
-        <v>14.01</v>
+        <v>12.26</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -2722,25 +2707,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" t="s">
         <v>117</v>
       </c>
-      <c r="B54" t="s">
-        <v>118</v>
-      </c>
       <c r="C54" s="1">
-        <v>12.15</v>
+        <v>13.69</v>
       </c>
       <c r="D54" s="1">
-        <v>11.91</v>
+        <v>13.46</v>
       </c>
       <c r="E54" s="1">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G54" s="1">
-        <v>11.91</v>
+        <v>13.46</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -2748,25 +2733,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" t="s">
         <v>119</v>
       </c>
-      <c r="B55" t="s">
-        <v>120</v>
-      </c>
       <c r="C55" s="1">
-        <v>12.5</v>
+        <v>13.55</v>
       </c>
       <c r="D55" s="1">
-        <v>12.26</v>
+        <v>13.33</v>
       </c>
       <c r="E55" s="1">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1">
-        <v>12.26</v>
+        <v>13.33</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -2774,25 +2759,25 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" t="s">
         <v>121</v>
       </c>
-      <c r="B56" t="s">
-        <v>122</v>
-      </c>
       <c r="C56" s="1">
-        <v>12.5</v>
+        <v>16.95</v>
       </c>
       <c r="D56" s="1">
-        <v>12.26</v>
+        <v>16.73</v>
       </c>
       <c r="E56" s="1">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G56" s="1">
-        <v>12.26</v>
+        <v>16.73</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -2800,25 +2785,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" t="s">
         <v>123</v>
       </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
       <c r="C57" s="1">
-        <v>13.69</v>
+        <v>21.99</v>
       </c>
       <c r="D57" s="1">
-        <v>13.46</v>
+        <v>21.77</v>
       </c>
       <c r="E57" s="1">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G57" s="1">
-        <v>13.46</v>
+        <v>21.77</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -2826,25 +2811,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" t="s">
         <v>125</v>
       </c>
-      <c r="B58" t="s">
-        <v>126</v>
-      </c>
       <c r="C58" s="1">
-        <v>13.55</v>
+        <v>15.25</v>
       </c>
       <c r="D58" s="1">
-        <v>13.33</v>
+        <v>15.05</v>
       </c>
       <c r="E58" s="1">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G58" s="1">
-        <v>13.33</v>
+        <v>15.05</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -2852,25 +2837,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" t="s">
         <v>127</v>
       </c>
-      <c r="B59" t="s">
-        <v>128</v>
-      </c>
       <c r="C59" s="1">
-        <v>16.95</v>
+        <v>13.25</v>
       </c>
       <c r="D59" s="1">
-        <v>16.73</v>
+        <v>13.06</v>
       </c>
       <c r="E59" s="1">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G59" s="1">
-        <v>16.73</v>
+        <v>13.06</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -2878,25 +2863,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" t="s">
         <v>129</v>
       </c>
-      <c r="B60" t="s">
-        <v>130</v>
-      </c>
       <c r="C60" s="1">
-        <v>21.99</v>
+        <v>13.19</v>
       </c>
       <c r="D60" s="1">
-        <v>21.77</v>
+        <v>13</v>
       </c>
       <c r="E60" s="1">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G60" s="1">
-        <v>21.77</v>
+        <v>13</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -2904,25 +2889,25 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" t="s">
         <v>131</v>
       </c>
-      <c r="B61" t="s">
-        <v>132</v>
-      </c>
       <c r="C61" s="1">
-        <v>15.25</v>
+        <v>14.25</v>
       </c>
       <c r="D61" s="1">
-        <v>15.05</v>
+        <v>14.06</v>
       </c>
       <c r="E61" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G61" s="1">
-        <v>15.05</v>
+        <v>14.06</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -2930,25 +2915,25 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" t="s">
         <v>133</v>
       </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
       <c r="C62" s="1">
-        <v>13.25</v>
+        <v>13.99</v>
       </c>
       <c r="D62" s="1">
-        <v>13.06</v>
+        <v>13.82</v>
       </c>
       <c r="E62" s="1">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G62" s="1">
-        <v>13.06</v>
+        <v>13.82</v>
       </c>
       <c r="H62" t="s">
         <v>11</v>
@@ -2956,25 +2941,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
         <v>135</v>
       </c>
-      <c r="B63" t="s">
-        <v>136</v>
-      </c>
       <c r="C63" s="1">
-        <v>13.19</v>
+        <v>13.95</v>
       </c>
       <c r="D63" s="1">
-        <v>13</v>
+        <v>13.78</v>
       </c>
       <c r="E63" s="1">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G63" s="1">
-        <v>13</v>
+        <v>13.78</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
@@ -2982,25 +2967,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" t="s">
         <v>137</v>
       </c>
-      <c r="B64" t="s">
-        <v>138</v>
-      </c>
       <c r="C64" s="1">
-        <v>14.25</v>
+        <v>13.95</v>
       </c>
       <c r="D64" s="1">
-        <v>14.06</v>
+        <v>13.78</v>
       </c>
       <c r="E64" s="1">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F64" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G64" s="1">
-        <v>14.06</v>
+        <v>13.78</v>
       </c>
       <c r="H64" t="s">
         <v>11</v>
@@ -3008,25 +2993,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
         <v>139</v>
       </c>
-      <c r="B65" t="s">
-        <v>140</v>
-      </c>
       <c r="C65" s="1">
-        <v>13.99</v>
+        <v>14.75</v>
       </c>
       <c r="D65" s="1">
-        <v>13.82</v>
+        <v>14.58</v>
       </c>
       <c r="E65" s="1">
         <v>0.17</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G65" s="1">
-        <v>13.82</v>
+        <v>14.58</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
@@ -3034,10 +3019,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" t="s">
         <v>141</v>
-      </c>
-      <c r="B66" t="s">
-        <v>142</v>
       </c>
       <c r="C66" s="1">
         <v>13.95</v>
@@ -3049,7 +3034,7 @@
         <v>0.17</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G66" s="1">
         <v>13.78</v>
@@ -3060,25 +3045,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" t="s">
         <v>143</v>
       </c>
-      <c r="B67" t="s">
-        <v>144</v>
-      </c>
       <c r="C67" s="1">
-        <v>13.95</v>
+        <v>14.75</v>
       </c>
       <c r="D67" s="1">
-        <v>13.78</v>
+        <v>14.58</v>
       </c>
       <c r="E67" s="1">
         <v>0.17</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G67" s="1">
-        <v>13.78</v>
+        <v>14.58</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -3086,25 +3071,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
       </c>
-      <c r="B68" t="s">
-        <v>146</v>
-      </c>
       <c r="C68" s="1">
-        <v>14.75</v>
+        <v>13.69</v>
       </c>
       <c r="D68" s="1">
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="E68" s="1">
         <v>0.17</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G68" s="1">
-        <v>14.58</v>
+        <v>13.52</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -3112,25 +3097,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>146</v>
+      </c>
+      <c r="B69" t="s">
         <v>147</v>
       </c>
-      <c r="B69" t="s">
-        <v>148</v>
-      </c>
       <c r="C69" s="1">
         <v>13.95</v>
       </c>
       <c r="D69" s="1">
-        <v>13.78</v>
+        <v>13.79</v>
       </c>
       <c r="E69" s="1">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G69" s="1">
-        <v>13.78</v>
+        <v>13.79</v>
       </c>
       <c r="H69" t="s">
         <v>11</v>
@@ -3138,25 +3123,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" t="s">
         <v>149</v>
       </c>
-      <c r="B70" t="s">
-        <v>150</v>
-      </c>
       <c r="C70" s="1">
-        <v>14.75</v>
+        <v>13.95</v>
       </c>
       <c r="D70" s="1">
-        <v>14.58</v>
+        <v>13.79</v>
       </c>
       <c r="E70" s="1">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G70" s="1">
-        <v>14.58</v>
+        <v>13.79</v>
       </c>
       <c r="H70" t="s">
         <v>11</v>
@@ -3164,25 +3149,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" t="s">
         <v>151</v>
       </c>
-      <c r="B71" t="s">
-        <v>152</v>
-      </c>
       <c r="C71" s="1">
-        <v>13.69</v>
+        <v>14.59</v>
       </c>
       <c r="D71" s="1">
-        <v>13.52</v>
+        <v>14.43</v>
       </c>
       <c r="E71" s="1">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G71" s="1">
-        <v>13.52</v>
+        <v>14.43</v>
       </c>
       <c r="H71" t="s">
         <v>11</v>
@@ -3190,10 +3175,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>154</v>
       </c>
       <c r="C72" s="1">
         <v>13.95</v>
@@ -3205,7 +3190,7 @@
         <v>0.16</v>
       </c>
       <c r="F72" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G72" s="1">
         <v>13.79</v>
@@ -3216,25 +3201,25 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
         <v>155</v>
       </c>
-      <c r="B73" t="s">
-        <v>156</v>
-      </c>
       <c r="C73" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D73" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="E73" s="1">
         <v>0.16</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G73" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="H73" t="s">
         <v>11</v>
@@ -3242,25 +3227,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" t="s">
         <v>157</v>
       </c>
-      <c r="B74" t="s">
-        <v>158</v>
-      </c>
       <c r="C74" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D74" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="E74" s="1">
         <v>0.16</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G74" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="H74" t="s">
         <v>11</v>
@@ -3268,25 +3253,25 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" t="s">
         <v>159</v>
       </c>
-      <c r="B75" t="s">
-        <v>160</v>
-      </c>
       <c r="C75" s="1">
-        <v>13.95</v>
+        <v>14.59</v>
       </c>
       <c r="D75" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="E75" s="1">
         <v>0.16</v>
       </c>
       <c r="F75" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G75" s="1">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
       <c r="H75" t="s">
         <v>11</v>
@@ -3294,10 +3279,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>160</v>
+      </c>
+      <c r="B76" t="s">
         <v>161</v>
-      </c>
-      <c r="B76" t="s">
-        <v>162</v>
       </c>
       <c r="C76" s="1">
         <v>14.59</v>
@@ -3309,7 +3294,7 @@
         <v>0.16</v>
       </c>
       <c r="F76" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G76" s="1">
         <v>14.43</v>
@@ -3320,25 +3305,25 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>162</v>
+      </c>
+      <c r="B77" t="s">
         <v>163</v>
       </c>
-      <c r="B77" t="s">
-        <v>164</v>
-      </c>
       <c r="C77" s="1">
-        <v>13.95</v>
+        <v>14.5</v>
       </c>
       <c r="D77" s="1">
-        <v>13.79</v>
+        <v>14.34</v>
       </c>
       <c r="E77" s="1">
         <v>0.16</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G77" s="1">
-        <v>13.79</v>
+        <v>14.34</v>
       </c>
       <c r="H77" t="s">
         <v>11</v>
@@ -3346,10 +3331,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" t="s">
         <v>165</v>
-      </c>
-      <c r="B78" t="s">
-        <v>166</v>
       </c>
       <c r="C78" s="1">
         <v>14.59</v>
@@ -3361,7 +3346,7 @@
         <v>0.16</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G78" s="1">
         <v>14.43</v>
@@ -3372,25 +3357,25 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" t="s">
         <v>167</v>
       </c>
-      <c r="B79" t="s">
-        <v>168</v>
-      </c>
       <c r="C79" s="1">
-        <v>14.59</v>
+        <v>13.95</v>
       </c>
       <c r="D79" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="E79" s="1">
         <v>0.16</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G79" s="1">
-        <v>14.43</v>
+        <v>13.79</v>
       </c>
       <c r="H79" t="s">
         <v>11</v>
@@ -3398,25 +3383,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B80" t="s">
         <v>169</v>
       </c>
-      <c r="B80" t="s">
-        <v>170</v>
-      </c>
       <c r="C80" s="1">
-        <v>14.5</v>
+        <v>13.95</v>
       </c>
       <c r="D80" s="1">
-        <v>14.34</v>
+        <v>13.79</v>
       </c>
       <c r="E80" s="1">
         <v>0.16</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G80" s="1">
-        <v>14.34</v>
+        <v>13.79</v>
       </c>
       <c r="H80" t="s">
         <v>11</v>
@@ -3424,10 +3409,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" t="s">
         <v>171</v>
-      </c>
-      <c r="B81" t="s">
-        <v>172</v>
       </c>
       <c r="C81" s="1">
         <v>14.59</v>
@@ -3439,7 +3424,7 @@
         <v>0.16</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G81" s="1">
         <v>14.43</v>
@@ -3450,25 +3435,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>172</v>
+      </c>
+      <c r="B82" t="s">
         <v>173</v>
       </c>
-      <c r="B82" t="s">
-        <v>174</v>
-      </c>
       <c r="C82" s="1">
-        <v>13.95</v>
+        <v>12.75</v>
       </c>
       <c r="D82" s="1">
-        <v>13.79</v>
+        <v>12.6</v>
       </c>
       <c r="E82" s="1">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F82" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G82" s="1">
-        <v>13.79</v>
+        <v>12.6</v>
       </c>
       <c r="H82" t="s">
         <v>11</v>
@@ -3476,25 +3461,25 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>174</v>
+      </c>
+      <c r="B83" t="s">
         <v>175</v>
       </c>
-      <c r="B83" t="s">
-        <v>176</v>
-      </c>
       <c r="C83" s="1">
-        <v>13.95</v>
+        <v>12.5</v>
       </c>
       <c r="D83" s="1">
-        <v>13.79</v>
+        <v>12.35</v>
       </c>
       <c r="E83" s="1">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G83" s="1">
-        <v>13.79</v>
+        <v>12.35</v>
       </c>
       <c r="H83" t="s">
         <v>11</v>
@@ -3502,25 +3487,25 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" t="s">
         <v>177</v>
       </c>
-      <c r="B84" t="s">
-        <v>178</v>
-      </c>
       <c r="C84" s="1">
-        <v>14.59</v>
+        <v>13.99</v>
       </c>
       <c r="D84" s="1">
-        <v>14.43</v>
+        <v>13.85</v>
       </c>
       <c r="E84" s="1">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G84" s="1">
-        <v>14.43</v>
+        <v>13.85</v>
       </c>
       <c r="H84" t="s">
         <v>11</v>
@@ -3528,25 +3513,25 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>178</v>
+      </c>
+      <c r="B85" t="s">
         <v>179</v>
       </c>
-      <c r="B85" t="s">
-        <v>180</v>
-      </c>
       <c r="C85" s="1">
-        <v>12.75</v>
+        <v>13.99</v>
       </c>
       <c r="D85" s="1">
-        <v>12.6</v>
+        <v>13.85</v>
       </c>
       <c r="E85" s="1">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G85" s="1">
-        <v>12.6</v>
+        <v>13.85</v>
       </c>
       <c r="H85" t="s">
         <v>11</v>
@@ -3554,25 +3539,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>180</v>
+      </c>
+      <c r="B86" t="s">
         <v>181</v>
       </c>
-      <c r="B86" t="s">
-        <v>182</v>
-      </c>
       <c r="C86" s="1">
-        <v>12.5</v>
+        <v>14.19</v>
       </c>
       <c r="D86" s="1">
-        <v>12.35</v>
+        <v>14.05</v>
       </c>
       <c r="E86" s="1">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G86" s="1">
-        <v>12.35</v>
+        <v>14.05</v>
       </c>
       <c r="H86" t="s">
         <v>11</v>
@@ -3580,25 +3565,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>182</v>
+      </c>
+      <c r="B87" t="s">
         <v>183</v>
       </c>
-      <c r="B87" t="s">
-        <v>184</v>
-      </c>
       <c r="C87" s="1">
-        <v>13.99</v>
+        <v>14.09</v>
       </c>
       <c r="D87" s="1">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="E87" s="1">
         <v>0.14</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G87" s="1">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="H87" t="s">
         <v>11</v>
@@ -3606,25 +3591,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>184</v>
+      </c>
+      <c r="B88" t="s">
         <v>185</v>
       </c>
-      <c r="B88" t="s">
-        <v>186</v>
-      </c>
       <c r="C88" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D88" s="1">
-        <v>13.85</v>
+        <v>13.81</v>
       </c>
       <c r="E88" s="1">
         <v>0.14</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G88" s="1">
-        <v>13.85</v>
+        <v>13.81</v>
       </c>
       <c r="H88" t="s">
         <v>11</v>
@@ -3632,10 +3617,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>186</v>
+      </c>
+      <c r="B89" t="s">
         <v>187</v>
-      </c>
-      <c r="B89" t="s">
-        <v>188</v>
       </c>
       <c r="C89" s="1">
         <v>14.19</v>
@@ -3647,7 +3632,7 @@
         <v>0.14</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G89" s="1">
         <v>14.05</v>
@@ -3658,25 +3643,25 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" t="s">
         <v>189</v>
       </c>
-      <c r="B90" t="s">
-        <v>190</v>
-      </c>
       <c r="C90" s="1">
-        <v>14.09</v>
+        <v>13.95</v>
       </c>
       <c r="D90" s="1">
-        <v>13.95</v>
+        <v>13.81</v>
       </c>
       <c r="E90" s="1">
         <v>0.14</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G90" s="1">
-        <v>13.95</v>
+        <v>13.81</v>
       </c>
       <c r="H90" t="s">
         <v>11</v>
@@ -3684,25 +3669,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>190</v>
+      </c>
+      <c r="B91" t="s">
         <v>191</v>
       </c>
-      <c r="B91" t="s">
-        <v>192</v>
-      </c>
       <c r="C91" s="1">
         <v>13.95</v>
       </c>
       <c r="D91" s="1">
-        <v>13.81</v>
+        <v>13.82</v>
       </c>
       <c r="E91" s="1">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G91" s="1">
-        <v>13.81</v>
+        <v>13.82</v>
       </c>
       <c r="H91" t="s">
         <v>11</v>
@@ -3710,25 +3695,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>192</v>
+      </c>
+      <c r="B92" t="s">
         <v>193</v>
       </c>
-      <c r="B92" t="s">
-        <v>194</v>
-      </c>
       <c r="C92" s="1">
-        <v>14.19</v>
+        <v>13.95</v>
       </c>
       <c r="D92" s="1">
-        <v>14.05</v>
+        <v>13.82</v>
       </c>
       <c r="E92" s="1">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F92" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G92" s="1">
-        <v>14.05</v>
+        <v>13.82</v>
       </c>
       <c r="H92" t="s">
         <v>11</v>
@@ -3736,25 +3721,25 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>194</v>
+      </c>
+      <c r="B93" t="s">
         <v>195</v>
       </c>
-      <c r="B93" t="s">
-        <v>196</v>
-      </c>
       <c r="C93" s="1">
-        <v>13.95</v>
+        <v>12.5</v>
       </c>
       <c r="D93" s="1">
-        <v>13.81</v>
+        <v>12.37</v>
       </c>
       <c r="E93" s="1">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G93" s="1">
-        <v>13.81</v>
+        <v>12.37</v>
       </c>
       <c r="H93" t="s">
         <v>11</v>
@@ -3762,10 +3747,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>196</v>
+      </c>
+      <c r="B94" t="s">
         <v>197</v>
-      </c>
-      <c r="B94" t="s">
-        <v>198</v>
       </c>
       <c r="C94" s="1">
         <v>13.95</v>
@@ -3777,7 +3762,7 @@
         <v>0.13</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G94" s="1">
         <v>13.82</v>
@@ -3788,25 +3773,25 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" t="s">
         <v>199</v>
       </c>
-      <c r="B95" t="s">
-        <v>200</v>
-      </c>
       <c r="C95" s="1">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="D95" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="E95" s="1">
         <v>0.13</v>
       </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G95" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="H95" t="s">
         <v>11</v>
@@ -3814,25 +3799,25 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s">
         <v>201</v>
       </c>
-      <c r="B96" t="s">
-        <v>202</v>
-      </c>
       <c r="C96" s="1">
-        <v>12.5</v>
+        <v>13.95</v>
       </c>
       <c r="D96" s="1">
-        <v>12.37</v>
+        <v>13.82</v>
       </c>
       <c r="E96" s="1">
         <v>0.13</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G96" s="1">
-        <v>12.37</v>
+        <v>13.82</v>
       </c>
       <c r="H96" t="s">
         <v>11</v>
@@ -3840,10 +3825,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>202</v>
+      </c>
+      <c r="B97" t="s">
         <v>203</v>
-      </c>
-      <c r="B97" t="s">
-        <v>204</v>
       </c>
       <c r="C97" s="1">
         <v>13.95</v>
@@ -3855,7 +3840,7 @@
         <v>0.13</v>
       </c>
       <c r="F97" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G97" s="1">
         <v>13.82</v>
@@ -3866,25 +3851,25 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>204</v>
+      </c>
+      <c r="B98" t="s">
         <v>205</v>
       </c>
-      <c r="B98" t="s">
-        <v>206</v>
-      </c>
       <c r="C98" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D98" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="E98" s="1">
         <v>0.13</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G98" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="H98" t="s">
         <v>11</v>
@@ -3892,25 +3877,25 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>206</v>
+      </c>
+      <c r="B99" t="s">
         <v>207</v>
       </c>
-      <c r="B99" t="s">
-        <v>208</v>
-      </c>
       <c r="C99" s="1">
-        <v>13.95</v>
+        <v>13.1</v>
       </c>
       <c r="D99" s="1">
-        <v>13.82</v>
+        <v>12.97</v>
       </c>
       <c r="E99" s="1">
         <v>0.13</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G99" s="1">
-        <v>13.82</v>
+        <v>12.97</v>
       </c>
       <c r="H99" t="s">
         <v>11</v>
@@ -3918,10 +3903,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" t="s">
         <v>209</v>
-      </c>
-      <c r="B100" t="s">
-        <v>210</v>
       </c>
       <c r="C100" s="1">
         <v>13.95</v>
@@ -3933,7 +3918,7 @@
         <v>0.13</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G100" s="1">
         <v>13.82</v>
@@ -3944,10 +3929,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" t="s">
         <v>211</v>
-      </c>
-      <c r="B101" t="s">
-        <v>212</v>
       </c>
       <c r="C101" s="1">
         <v>13.95</v>
@@ -3959,7 +3944,7 @@
         <v>0.13</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G101" s="1">
         <v>13.82</v>
@@ -3970,25 +3955,25 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>212</v>
+      </c>
+      <c r="B102" t="s">
         <v>213</v>
       </c>
-      <c r="B102" t="s">
-        <v>214</v>
-      </c>
       <c r="C102" s="1">
-        <v>13.1</v>
+        <v>13.95</v>
       </c>
       <c r="D102" s="1">
-        <v>12.97</v>
+        <v>13.82</v>
       </c>
       <c r="E102" s="1">
         <v>0.13</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G102" s="1">
-        <v>12.97</v>
+        <v>13.82</v>
       </c>
       <c r="H102" t="s">
         <v>11</v>
@@ -3996,10 +3981,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" t="s">
         <v>215</v>
-      </c>
-      <c r="B103" t="s">
-        <v>216</v>
       </c>
       <c r="C103" s="1">
         <v>13.95</v>
@@ -4011,7 +3996,7 @@
         <v>0.13</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G103" s="1">
         <v>13.82</v>
@@ -4022,10 +4007,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" t="s">
         <v>217</v>
-      </c>
-      <c r="B104" t="s">
-        <v>218</v>
       </c>
       <c r="C104" s="1">
         <v>13.95</v>
@@ -4037,7 +4022,7 @@
         <v>0.13</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G104" s="1">
         <v>13.82</v>
@@ -4048,10 +4033,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" t="s">
         <v>219</v>
-      </c>
-      <c r="B105" t="s">
-        <v>220</v>
       </c>
       <c r="C105" s="1">
         <v>13.95</v>
@@ -4063,7 +4048,7 @@
         <v>0.13</v>
       </c>
       <c r="F105" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G105" s="1">
         <v>13.82</v>
@@ -4074,10 +4059,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" t="s">
         <v>221</v>
-      </c>
-      <c r="B106" t="s">
-        <v>222</v>
       </c>
       <c r="C106" s="1">
         <v>13.95</v>
@@ -4089,7 +4074,7 @@
         <v>0.13</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G106" s="1">
         <v>13.82</v>
@@ -4100,10 +4085,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>222</v>
+      </c>
+      <c r="B107" t="s">
         <v>223</v>
-      </c>
-      <c r="B107" t="s">
-        <v>224</v>
       </c>
       <c r="C107" s="1">
         <v>13.95</v>
@@ -4115,7 +4100,7 @@
         <v>0.13</v>
       </c>
       <c r="F107" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G107" s="1">
         <v>13.82</v>
@@ -4126,10 +4111,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" t="s">
         <v>225</v>
-      </c>
-      <c r="B108" t="s">
-        <v>226</v>
       </c>
       <c r="C108" s="1">
         <v>13.95</v>
@@ -4141,7 +4126,7 @@
         <v>0.13</v>
       </c>
       <c r="F108" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G108" s="1">
         <v>13.82</v>
@@ -4152,10 +4137,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" t="s">
         <v>227</v>
-      </c>
-      <c r="B109" t="s">
-        <v>228</v>
       </c>
       <c r="C109" s="1">
         <v>13.95</v>
@@ -4167,7 +4152,7 @@
         <v>0.13</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G109" s="1">
         <v>13.82</v>
@@ -4178,10 +4163,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" t="s">
         <v>229</v>
-      </c>
-      <c r="B110" t="s">
-        <v>230</v>
       </c>
       <c r="C110" s="1">
         <v>13.95</v>
@@ -4193,7 +4178,7 @@
         <v>0.13</v>
       </c>
       <c r="F110" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G110" s="1">
         <v>13.82</v>
@@ -4204,10 +4189,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" t="s">
         <v>231</v>
-      </c>
-      <c r="B111" t="s">
-        <v>232</v>
       </c>
       <c r="C111" s="1">
         <v>13.95</v>
@@ -4219,7 +4204,7 @@
         <v>0.13</v>
       </c>
       <c r="F111" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G111" s="1">
         <v>13.82</v>
@@ -4230,10 +4215,10 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>232</v>
+      </c>
+      <c r="B112" t="s">
         <v>233</v>
-      </c>
-      <c r="B112" t="s">
-        <v>234</v>
       </c>
       <c r="C112" s="1">
         <v>13.95</v>
@@ -4245,7 +4230,7 @@
         <v>0.13</v>
       </c>
       <c r="F112" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G112" s="1">
         <v>13.82</v>
@@ -4256,25 +4241,25 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>234</v>
+      </c>
+      <c r="B113" t="s">
         <v>235</v>
       </c>
-      <c r="B113" t="s">
-        <v>236</v>
-      </c>
       <c r="C113" s="1">
-        <v>13.95</v>
+        <v>13.99</v>
       </c>
       <c r="D113" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="E113" s="1">
         <v>0.13</v>
       </c>
       <c r="F113" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G113" s="1">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="H113" t="s">
         <v>11</v>
@@ -4282,10 +4267,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>236</v>
+      </c>
+      <c r="B114" t="s">
         <v>237</v>
-      </c>
-      <c r="B114" t="s">
-        <v>238</v>
       </c>
       <c r="C114" s="1">
         <v>13.95</v>
@@ -4297,7 +4282,7 @@
         <v>0.13</v>
       </c>
       <c r="F114" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G114" s="1">
         <v>13.82</v>
@@ -4308,10 +4293,10 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>238</v>
+      </c>
+      <c r="B115" t="s">
         <v>239</v>
-      </c>
-      <c r="B115" t="s">
-        <v>240</v>
       </c>
       <c r="C115" s="1">
         <v>13.95</v>
@@ -4323,7 +4308,7 @@
         <v>0.13</v>
       </c>
       <c r="F115" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G115" s="1">
         <v>13.82</v>
@@ -4334,25 +4319,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>240</v>
+      </c>
+      <c r="B116" t="s">
         <v>241</v>
       </c>
-      <c r="B116" t="s">
-        <v>242</v>
-      </c>
       <c r="C116" s="1">
-        <v>13.99</v>
+        <v>13.95</v>
       </c>
       <c r="D116" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="E116" s="1">
         <v>0.13</v>
       </c>
       <c r="F116" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G116" s="1">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="H116" t="s">
         <v>11</v>
@@ -4360,10 +4345,10 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>242</v>
+      </c>
+      <c r="B117" t="s">
         <v>243</v>
-      </c>
-      <c r="B117" t="s">
-        <v>244</v>
       </c>
       <c r="C117" s="1">
         <v>13.95</v>
@@ -4375,7 +4360,7 @@
         <v>0.13</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G117" s="1">
         <v>13.82</v>
@@ -4386,10 +4371,10 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>244</v>
+      </c>
+      <c r="B118" t="s">
         <v>245</v>
-      </c>
-      <c r="B118" t="s">
-        <v>246</v>
       </c>
       <c r="C118" s="1">
         <v>13.95</v>
@@ -4401,7 +4386,7 @@
         <v>0.13</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G118" s="1">
         <v>13.82</v>
@@ -4412,10 +4397,10 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" t="s">
         <v>247</v>
-      </c>
-      <c r="B119" t="s">
-        <v>248</v>
       </c>
       <c r="C119" s="1">
         <v>13.95</v>
@@ -4427,7 +4412,7 @@
         <v>0.13</v>
       </c>
       <c r="F119" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G119" s="1">
         <v>13.82</v>
@@ -4438,10 +4423,10 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>248</v>
+      </c>
+      <c r="B120" t="s">
         <v>249</v>
-      </c>
-      <c r="B120" t="s">
-        <v>250</v>
       </c>
       <c r="C120" s="1">
         <v>13.95</v>
@@ -4453,7 +4438,7 @@
         <v>0.13</v>
       </c>
       <c r="F120" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G120" s="1">
         <v>13.82</v>
@@ -4464,25 +4449,25 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>250</v>
+      </c>
+      <c r="B121" t="s">
         <v>251</v>
       </c>
-      <c r="B121" t="s">
-        <v>252</v>
-      </c>
       <c r="C121" s="1">
-        <v>13.95</v>
+        <v>14.09</v>
       </c>
       <c r="D121" s="1">
-        <v>13.82</v>
+        <v>13.96</v>
       </c>
       <c r="E121" s="1">
         <v>0.13</v>
       </c>
       <c r="F121" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G121" s="1">
-        <v>13.82</v>
+        <v>13.96</v>
       </c>
       <c r="H121" t="s">
         <v>11</v>
@@ -4490,10 +4475,10 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>252</v>
+      </c>
+      <c r="B122" t="s">
         <v>253</v>
-      </c>
-      <c r="B122" t="s">
-        <v>254</v>
       </c>
       <c r="C122" s="1">
         <v>13.95</v>
@@ -4505,7 +4490,7 @@
         <v>0.13</v>
       </c>
       <c r="F122" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G122" s="1">
         <v>13.82</v>
@@ -4516,25 +4501,25 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>254</v>
+      </c>
+      <c r="B123" t="s">
         <v>255</v>
       </c>
-      <c r="B123" t="s">
-        <v>256</v>
-      </c>
       <c r="C123" s="1">
-        <v>13.95</v>
+        <v>13.89</v>
       </c>
       <c r="D123" s="1">
-        <v>13.82</v>
+        <v>13.76</v>
       </c>
       <c r="E123" s="1">
         <v>0.13</v>
       </c>
       <c r="F123" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G123" s="1">
-        <v>13.82</v>
+        <v>13.76</v>
       </c>
       <c r="H123" t="s">
         <v>11</v>
@@ -4542,25 +4527,25 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>256</v>
+      </c>
+      <c r="B124" t="s">
         <v>257</v>
       </c>
-      <c r="B124" t="s">
-        <v>258</v>
-      </c>
       <c r="C124" s="1">
-        <v>14.09</v>
+        <v>12.45</v>
       </c>
       <c r="D124" s="1">
-        <v>13.96</v>
+        <v>12.33</v>
       </c>
       <c r="E124" s="1">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F124" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G124" s="1">
-        <v>13.96</v>
+        <v>12.33</v>
       </c>
       <c r="H124" t="s">
         <v>11</v>
@@ -4568,25 +4553,25 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>258</v>
+      </c>
+      <c r="B125" t="s">
         <v>259</v>
       </c>
-      <c r="B125" t="s">
-        <v>260</v>
-      </c>
       <c r="C125" s="1">
-        <v>13.95</v>
+        <v>12.5</v>
       </c>
       <c r="D125" s="1">
-        <v>13.82</v>
+        <v>12.38</v>
       </c>
       <c r="E125" s="1">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F125" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G125" s="1">
-        <v>13.82</v>
+        <v>12.38</v>
       </c>
       <c r="H125" t="s">
         <v>11</v>
@@ -4594,25 +4579,25 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>260</v>
+      </c>
+      <c r="B126" t="s">
         <v>261</v>
       </c>
-      <c r="B126" t="s">
-        <v>262</v>
-      </c>
       <c r="C126" s="1">
-        <v>13.89</v>
+        <v>12.5</v>
       </c>
       <c r="D126" s="1">
-        <v>13.76</v>
+        <v>12.38</v>
       </c>
       <c r="E126" s="1">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F126" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G126" s="1">
-        <v>13.76</v>
+        <v>12.38</v>
       </c>
       <c r="H126" t="s">
         <v>11</v>
@@ -4620,10 +4605,10 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>262</v>
+      </c>
+      <c r="B127" t="s">
         <v>263</v>
-      </c>
-      <c r="B127" t="s">
-        <v>264</v>
       </c>
       <c r="C127" s="1">
         <v>12.45</v>
@@ -4635,7 +4620,7 @@
         <v>0.12</v>
       </c>
       <c r="F127" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G127" s="1">
         <v>12.33</v>
@@ -4646,25 +4631,25 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>264</v>
+      </c>
+      <c r="B128" t="s">
         <v>265</v>
       </c>
-      <c r="B128" t="s">
-        <v>266</v>
-      </c>
       <c r="C128" s="1">
-        <v>12.5</v>
+        <v>13.59</v>
       </c>
       <c r="D128" s="1">
-        <v>12.38</v>
+        <v>13.47</v>
       </c>
       <c r="E128" s="1">
         <v>0.12</v>
       </c>
       <c r="F128" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G128" s="1">
-        <v>12.38</v>
+        <v>13.47</v>
       </c>
       <c r="H128" t="s">
         <v>11</v>
@@ -4672,25 +4657,25 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>266</v>
+      </c>
+      <c r="B129" t="s">
         <v>267</v>
       </c>
-      <c r="B129" t="s">
-        <v>268</v>
-      </c>
       <c r="C129" s="1">
-        <v>12.5</v>
+        <v>14.95</v>
       </c>
       <c r="D129" s="1">
-        <v>12.38</v>
+        <v>14.84</v>
       </c>
       <c r="E129" s="1">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F129" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G129" s="1">
-        <v>12.38</v>
+        <v>14.84</v>
       </c>
       <c r="H129" t="s">
         <v>11</v>
@@ -4698,25 +4683,25 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>268</v>
+      </c>
+      <c r="B130" t="s">
         <v>269</v>
       </c>
-      <c r="B130" t="s">
-        <v>270</v>
-      </c>
       <c r="C130" s="1">
-        <v>12.45</v>
+        <v>21.99</v>
       </c>
       <c r="D130" s="1">
-        <v>12.33</v>
+        <v>21.88</v>
       </c>
       <c r="E130" s="1">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F130" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G130" s="1">
-        <v>12.33</v>
+        <v>21.88</v>
       </c>
       <c r="H130" t="s">
         <v>11</v>
@@ -4724,25 +4709,25 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>270</v>
+      </c>
+      <c r="B131" t="s">
         <v>271</v>
       </c>
-      <c r="B131" t="s">
-        <v>272</v>
-      </c>
       <c r="C131" s="1">
-        <v>13.59</v>
+        <v>21.99</v>
       </c>
       <c r="D131" s="1">
-        <v>13.47</v>
+        <v>21.88</v>
       </c>
       <c r="E131" s="1">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G131" s="1">
-        <v>13.47</v>
+        <v>21.88</v>
       </c>
       <c r="H131" t="s">
         <v>11</v>
@@ -4750,25 +4735,25 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>272</v>
+      </c>
+      <c r="B132" t="s">
         <v>273</v>
       </c>
-      <c r="B132" t="s">
-        <v>274</v>
-      </c>
       <c r="C132" s="1">
-        <v>14.95</v>
+        <v>13.25</v>
       </c>
       <c r="D132" s="1">
-        <v>14.84</v>
+        <v>13.15</v>
       </c>
       <c r="E132" s="1">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G132" s="1">
-        <v>14.84</v>
+        <v>13.15</v>
       </c>
       <c r="H132" t="s">
         <v>11</v>
@@ -4776,25 +4761,25 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>274</v>
+      </c>
+      <c r="B133" t="s">
         <v>275</v>
-      </c>
-      <c r="B133" t="s">
-        <v>276</v>
       </c>
       <c r="C133" s="1">
         <v>21.99</v>
       </c>
       <c r="D133" s="1">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="E133" s="1">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G133" s="1">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="H133" t="s">
         <v>11</v>
@@ -4802,25 +4787,25 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>276</v>
+      </c>
+      <c r="B134" t="s">
         <v>277</v>
-      </c>
-      <c r="B134" t="s">
-        <v>278</v>
       </c>
       <c r="C134" s="1">
         <v>21.99</v>
       </c>
       <c r="D134" s="1">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="E134" s="1">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F134" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G134" s="1">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="H134" t="s">
         <v>11</v>
@@ -4828,25 +4813,25 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>278</v>
+      </c>
+      <c r="B135" t="s">
         <v>279</v>
       </c>
-      <c r="B135" t="s">
-        <v>280</v>
-      </c>
       <c r="C135" s="1">
-        <v>13.25</v>
+        <v>13.43</v>
       </c>
       <c r="D135" s="1">
-        <v>13.15</v>
+        <v>13.33</v>
       </c>
       <c r="E135" s="1">
         <v>0.1</v>
       </c>
       <c r="F135" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G135" s="1">
-        <v>13.15</v>
+        <v>13.33</v>
       </c>
       <c r="H135" t="s">
         <v>11</v>
@@ -4854,25 +4839,25 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>280</v>
+      </c>
+      <c r="B136" t="s">
         <v>281</v>
       </c>
-      <c r="B136" t="s">
-        <v>282</v>
-      </c>
       <c r="C136" s="1">
-        <v>21.99</v>
+        <v>13.29</v>
       </c>
       <c r="D136" s="1">
-        <v>21.89</v>
+        <v>13.2</v>
       </c>
       <c r="E136" s="1">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G136" s="1">
-        <v>21.89</v>
+        <v>13.2</v>
       </c>
       <c r="H136" t="s">
         <v>11</v>
@@ -4880,25 +4865,25 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>282</v>
+      </c>
+      <c r="B137" t="s">
         <v>283</v>
       </c>
-      <c r="B137" t="s">
-        <v>284</v>
-      </c>
       <c r="C137" s="1">
-        <v>21.99</v>
+        <v>12.69</v>
       </c>
       <c r="D137" s="1">
-        <v>21.89</v>
+        <v>12.6</v>
       </c>
       <c r="E137" s="1">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F137" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G137" s="1">
-        <v>21.89</v>
+        <v>12.6</v>
       </c>
       <c r="H137" t="s">
         <v>11</v>
@@ -4906,25 +4891,25 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>284</v>
+      </c>
+      <c r="B138" t="s">
         <v>285</v>
       </c>
-      <c r="B138" t="s">
-        <v>286</v>
-      </c>
       <c r="C138" s="1">
-        <v>13.43</v>
+        <v>12.99</v>
       </c>
       <c r="D138" s="1">
-        <v>13.33</v>
+        <v>12.91</v>
       </c>
       <c r="E138" s="1">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F138" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G138" s="1">
-        <v>13.33</v>
+        <v>12.91</v>
       </c>
       <c r="H138" t="s">
         <v>11</v>
@@ -4932,25 +4917,25 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>286</v>
+      </c>
+      <c r="B139" t="s">
         <v>287</v>
       </c>
-      <c r="B139" t="s">
-        <v>288</v>
-      </c>
       <c r="C139" s="1">
-        <v>13.29</v>
+        <v>12.95</v>
       </c>
       <c r="D139" s="1">
-        <v>13.2</v>
+        <v>12.87</v>
       </c>
       <c r="E139" s="1">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G139" s="1">
-        <v>13.2</v>
+        <v>12.87</v>
       </c>
       <c r="H139" t="s">
         <v>11</v>
@@ -4958,25 +4943,25 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>288</v>
+      </c>
+      <c r="B140" t="s">
         <v>289</v>
       </c>
-      <c r="B140" t="s">
-        <v>290</v>
-      </c>
       <c r="C140" s="1">
-        <v>12.69</v>
+        <v>12.19</v>
       </c>
       <c r="D140" s="1">
-        <v>12.6</v>
+        <v>12.12</v>
       </c>
       <c r="E140" s="1">
-        <v>0.09</v>
+        <v>0.07</v>
       </c>
       <c r="F140" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G140" s="1">
-        <v>12.6</v>
+        <v>12.12</v>
       </c>
       <c r="H140" t="s">
         <v>11</v>
@@ -4984,25 +4969,25 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>290</v>
+      </c>
+      <c r="B141" t="s">
         <v>291</v>
       </c>
-      <c r="B141" t="s">
-        <v>292</v>
-      </c>
       <c r="C141" s="1">
-        <v>12.99</v>
+        <v>12.45</v>
       </c>
       <c r="D141" s="1">
-        <v>12.91</v>
+        <v>12.39</v>
       </c>
       <c r="E141" s="1">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F141" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G141" s="1">
-        <v>12.91</v>
+        <v>12.39</v>
       </c>
       <c r="H141" t="s">
         <v>11</v>
@@ -5010,25 +4995,25 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>292</v>
+      </c>
+      <c r="B142" t="s">
         <v>293</v>
       </c>
-      <c r="B142" t="s">
-        <v>294</v>
-      </c>
       <c r="C142" s="1">
-        <v>12.95</v>
+        <v>14.59</v>
       </c>
       <c r="D142" s="1">
-        <v>12.87</v>
+        <v>14.54</v>
       </c>
       <c r="E142" s="1">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F142" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G142" s="1">
-        <v>12.87</v>
+        <v>14.54</v>
       </c>
       <c r="H142" t="s">
         <v>11</v>
@@ -5036,25 +5021,25 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>294</v>
+      </c>
+      <c r="B143" t="s">
         <v>295</v>
       </c>
-      <c r="B143" t="s">
-        <v>296</v>
-      </c>
       <c r="C143" s="1">
-        <v>12.45</v>
+        <v>14.95</v>
       </c>
       <c r="D143" s="1">
-        <v>12.39</v>
+        <v>14.9</v>
       </c>
       <c r="E143" s="1">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F143" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G143" s="1">
-        <v>12.39</v>
+        <v>14.9</v>
       </c>
       <c r="H143" t="s">
         <v>11</v>
@@ -5062,25 +5047,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>296</v>
+      </c>
+      <c r="B144" t="s">
         <v>297</v>
       </c>
-      <c r="B144" t="s">
-        <v>298</v>
-      </c>
       <c r="C144" s="1">
-        <v>14.59</v>
+        <v>11.59</v>
       </c>
       <c r="D144" s="1">
-        <v>14.54</v>
+        <v>11.54</v>
       </c>
       <c r="E144" s="1">
         <v>0.05</v>
       </c>
       <c r="F144" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G144" s="1">
-        <v>14.54</v>
+        <v>11.54</v>
       </c>
       <c r="H144" t="s">
         <v>11</v>
@@ -5088,25 +5073,25 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>298</v>
+      </c>
+      <c r="B145" t="s">
         <v>299</v>
       </c>
-      <c r="B145" t="s">
-        <v>300</v>
-      </c>
       <c r="C145" s="1">
-        <v>14.95</v>
+        <v>11.59</v>
       </c>
       <c r="D145" s="1">
-        <v>14.9</v>
+        <v>11.54</v>
       </c>
       <c r="E145" s="1">
         <v>0.05</v>
       </c>
       <c r="F145" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G145" s="1">
-        <v>14.9</v>
+        <v>11.54</v>
       </c>
       <c r="H145" t="s">
         <v>11</v>
@@ -5114,25 +5099,25 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>300</v>
+      </c>
+      <c r="B146" t="s">
         <v>301</v>
       </c>
-      <c r="B146" t="s">
-        <v>302</v>
-      </c>
       <c r="C146" s="1">
-        <v>11.59</v>
+        <v>11.55</v>
       </c>
       <c r="D146" s="1">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="E146" s="1">
         <v>0.05</v>
       </c>
       <c r="F146" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G146" s="1">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="H146" t="s">
         <v>11</v>
@@ -5140,79 +5125,27 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>302</v>
+      </c>
+      <c r="B147" t="s">
         <v>303</v>
       </c>
-      <c r="B147" t="s">
-        <v>304</v>
-      </c>
       <c r="C147" s="1">
-        <v>11.59</v>
+        <v>19.99</v>
       </c>
       <c r="D147" s="1">
-        <v>11.54</v>
+        <v>19.95</v>
       </c>
       <c r="E147" s="1">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F147" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G147" s="1">
-        <v>11.54</v>
+        <v>19.95</v>
       </c>
       <c r="H147" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>305</v>
-      </c>
-      <c r="B148" t="s">
-        <v>306</v>
-      </c>
-      <c r="C148" s="1">
-        <v>11.55</v>
-      </c>
-      <c r="D148" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="E148" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F148" t="s">
-        <v>10</v>
-      </c>
-      <c r="G148" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="H148" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>307</v>
-      </c>
-      <c r="B149" t="s">
-        <v>308</v>
-      </c>
-      <c r="C149" s="1">
-        <v>19.99</v>
-      </c>
-      <c r="D149" s="1">
-        <v>19.95</v>
-      </c>
-      <c r="E149" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F149" t="s">
-        <v>10</v>
-      </c>
-      <c r="G149" s="1">
-        <v>19.95</v>
-      </c>
-      <c r="H149" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-NL-2026-05-16.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="151">
   <si>
     <t>Product</t>
   </si>
@@ -37,6 +37,84 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Omerta - Wild Poppy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380023</t>
+  </si>
+  <si>
+    <t>Tvserieshop</t>
+  </si>
+  <si>
+    <t>FBR</t>
+  </si>
+  <si>
+    <t>Omerta - Royal X - Eau de toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370260</t>
+  </si>
+  <si>
+    <t>Colorful Shoe Shoe Pack</t>
+  </si>
+  <si>
+    <t>8720938379253</t>
+  </si>
+  <si>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta - Night Power Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379284</t>
+  </si>
+  <si>
+    <t>Omerta - Oud &amp; Class Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379307</t>
+  </si>
+  <si>
+    <t>Omerta - Wild energy Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379291</t>
+  </si>
+  <si>
+    <t>Omerta - Night Out Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379239</t>
+  </si>
+  <si>
+    <t>Omerta - Daily Elegance Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379222</t>
+  </si>
+  <si>
+    <t>Omerta - Seduction Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379260</t>
+  </si>
+  <si>
+    <t>Omerta - Signature Pack - set van 3x100ml</t>
+  </si>
+  <si>
+    <t>8720938379314</t>
+  </si>
+  <si>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>6291012000261</t>
+  </si>
+  <si>
+    <t>Dorsh</t>
+  </si>
+  <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
   </si>
   <si>
@@ -46,7 +124,16 @@
     <t>Juwelium</t>
   </si>
   <si>
-    <t>FBR</t>
+    <t>Azira - Royal Oud - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102720</t>
+  </si>
+  <si>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102706</t>
   </si>
   <si>
     <t>Hello Kitty Rainbow Eau de Parfum voor Kinderen 50ml</t>
@@ -58,6 +145,168 @@
     <t>Koopjesfun.nl</t>
   </si>
   <si>
+    <t>Sentio Vintage Forrest Unisex Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8721055491477</t>
+  </si>
+  <si>
+    <t>Sentio What Happens Under The Mistletoe Stays Under The Mistletoe - Eau de parfum</t>
+  </si>
+  <si>
+    <t>8721055492795</t>
+  </si>
+  <si>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
+    <t>8719214757229</t>
+  </si>
+  <si>
+    <t>NG Embodiment of Style Women Eau de Parfum Spray 100 ml</t>
+  </si>
+  <si>
+    <t>8719214752576</t>
+  </si>
+  <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658999430</t>
+  </si>
+  <si>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380931</t>
+  </si>
+  <si>
+    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
+  </si>
+  <si>
+    <t>8715658370086</t>
+  </si>
+  <si>
+    <t>Omerta - Golden challenge EDT men 100 ml</t>
+  </si>
+  <si>
+    <t>8720938379345</t>
+  </si>
+  <si>
+    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658380351</t>
+  </si>
+  <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370505</t>
+  </si>
+  <si>
+    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380221</t>
+  </si>
+  <si>
+    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
+  </si>
+  <si>
+    <t>8720938379352</t>
+  </si>
+  <si>
+    <t>Omerta - Royal X Red - EDT men 100ml</t>
+  </si>
+  <si>
+    <t>8715658370369</t>
+  </si>
+  <si>
+    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658999638</t>
+  </si>
+  <si>
+    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370543</t>
+  </si>
+  <si>
+    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380757</t>
+  </si>
+  <si>
+    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380405</t>
+  </si>
+  <si>
+    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380672</t>
+  </si>
+  <si>
+    <t>Omerta - Sensible Man - EDT men - 100ml</t>
+  </si>
+  <si>
+    <t>8715658999249</t>
+  </si>
+  <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380115</t>
+  </si>
+  <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658998839</t>
+  </si>
+  <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658997993</t>
+  </si>
+  <si>
+    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8715658380665</t>
+  </si>
+  <si>
+    <t>Omerta - Golden Challenge Elixer - 1EDT men 100ml</t>
+  </si>
+  <si>
+    <t>8715658370437</t>
+  </si>
+  <si>
+    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
+  </si>
+  <si>
+    <t>8715658380658</t>
+  </si>
+  <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>8715658370062</t>
+  </si>
+  <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
+    <t>8715658380580</t>
+  </si>
+  <si>
     <t>Real Time - Oú sont les - Eau de parfum - 100 ml</t>
   </si>
   <si>
@@ -70,15 +319,21 @@
     <t>8715658997764</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
     <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
     <t>8721055494225</t>
   </si>
   <si>
-    <t>Minimarkt W&amp;M</t>
-  </si>
-  <si>
     <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -115,6 +370,12 @@
     <t>8721055494232</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493891</t>
+  </si>
+  <si>
     <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -145,6 +406,12 @@
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493884</t>
+  </si>
+  <si>
     <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -157,6 +424,18 @@
     <t>7640158816813</t>
   </si>
   <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493853</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493877</t>
+  </si>
+  <si>
     <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -179,6 +458,12 @@
   </si>
   <si>
     <t>8721055493723</t>
+  </si>
+  <si>
+    <t>Real Time - Fine Gold Pink Vibrations - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658361015</t>
   </si>
 </sst>
 </file>
@@ -570,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -617,19 +902,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>9.94</v>
+        <v>13.75</v>
       </c>
       <c r="D2" s="1">
-        <v>9.48</v>
+        <v>9.99</v>
       </c>
       <c r="E2" s="1">
-        <v>0.46</v>
+        <v>3.76</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>9.48</v>
+        <v>9.99</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -643,19 +928,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>13.95</v>
+        <v>11.5</v>
       </c>
       <c r="D3" s="1">
-        <v>13.62</v>
+        <v>9.99</v>
       </c>
       <c r="E3" s="1">
-        <v>0.33</v>
+        <v>1.51</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>13.62</v>
+        <v>9.99</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -663,25 +948,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
       <c r="C4" s="1">
-        <v>13.95</v>
+        <v>17.45</v>
       </c>
       <c r="D4" s="1">
-        <v>13.68</v>
+        <v>15.95</v>
       </c>
       <c r="E4" s="1">
-        <v>0.27</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1">
-        <v>13.68</v>
+        <v>15.95</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -695,19 +980,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>13.95</v>
+        <v>16.95</v>
       </c>
       <c r="D5" s="1">
-        <v>13.68</v>
+        <v>15.95</v>
       </c>
       <c r="E5" s="1">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1">
-        <v>13.68</v>
+        <v>15.95</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -721,19 +1006,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>5.25</v>
+        <v>16.95</v>
       </c>
       <c r="D6" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E6" s="1">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -741,25 +1026,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="1">
-        <v>5.25</v>
+        <v>16.95</v>
       </c>
       <c r="D7" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E7" s="1">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -767,25 +1052,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" s="1">
-        <v>5.25</v>
+        <v>16.95</v>
       </c>
       <c r="D8" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E8" s="1">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -793,25 +1078,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="1">
-        <v>5.25</v>
+        <v>16.95</v>
       </c>
       <c r="D9" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E9" s="1">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -819,25 +1104,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
       <c r="C10" s="1">
-        <v>5.25</v>
+        <v>16.95</v>
       </c>
       <c r="D10" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E10" s="1">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -845,25 +1130,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" s="1">
-        <v>5.25</v>
+        <v>16.89</v>
       </c>
       <c r="D11" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="E11" s="1">
-        <v>0.26</v>
+        <v>0.94</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1">
-        <v>4.99</v>
+        <v>15.95</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -871,25 +1156,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.31</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D12" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
       <c r="G12" s="1">
-        <v>4.99</v>
+        <v>9.31</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -903,19 +1188,19 @@
         <v>35</v>
       </c>
       <c r="C13" s="1">
-        <v>5.25</v>
+        <v>9.94</v>
       </c>
       <c r="D13" s="1">
-        <v>4.99</v>
+        <v>9.48</v>
       </c>
       <c r="E13" s="1">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1">
-        <v>4.99</v>
+        <v>9.48</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -923,25 +1208,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1">
-        <v>5.25</v>
+        <v>14.05</v>
       </c>
       <c r="D14" s="1">
-        <v>4.99</v>
+        <v>13.66</v>
       </c>
       <c r="E14" s="1">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G14" s="1">
-        <v>4.99</v>
+        <v>13.66</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -949,25 +1234,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
-        <v>5.25</v>
+        <v>14.25</v>
       </c>
       <c r="D15" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="E15" s="1">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1">
-        <v>4.99</v>
+        <v>13.91</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -975,25 +1260,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D16" s="1">
-        <v>4.99</v>
+        <v>13.62</v>
       </c>
       <c r="E16" s="1">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1">
-        <v>4.99</v>
+        <v>13.62</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1001,25 +1286,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1">
+        <v>13.89</v>
+      </c>
+      <c r="D17" s="1">
+        <v>13.56</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="F17" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D17" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
       <c r="G17" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1027,25 +1312,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1">
-        <v>5.25</v>
+        <v>8.25</v>
       </c>
       <c r="D18" s="1">
-        <v>4.99</v>
+        <v>7.92</v>
       </c>
       <c r="E18" s="1">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G18" s="1">
-        <v>4.99</v>
+        <v>7.92</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1053,25 +1338,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1">
-        <v>5.25</v>
+        <v>9.79</v>
       </c>
       <c r="D19" s="1">
-        <v>4.99</v>
+        <v>9.47</v>
       </c>
       <c r="E19" s="1">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G19" s="1">
-        <v>4.99</v>
+        <v>9.47</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -1079,25 +1364,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1">
-        <v>5.25</v>
+        <v>12.5</v>
       </c>
       <c r="D20" s="1">
-        <v>4.99</v>
+        <v>12.2</v>
       </c>
       <c r="E20" s="1">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G20" s="1">
-        <v>4.99</v>
+        <v>12.2</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1105,25 +1390,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1">
-        <v>5.25</v>
+        <v>9.79</v>
       </c>
       <c r="D21" s="1">
-        <v>4.99</v>
+        <v>9.5</v>
       </c>
       <c r="E21" s="1">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1">
-        <v>4.99</v>
+        <v>9.5</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1131,25 +1416,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1">
-        <v>12.75</v>
+        <v>9.79</v>
       </c>
       <c r="D22" s="1">
-        <v>12.51</v>
+        <v>9.5</v>
       </c>
       <c r="E22" s="1">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1">
-        <v>12.51</v>
+        <v>9.5</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1157,27 +1442,1223 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D28" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D32" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D33" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D34" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D35" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D36" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D38" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D41" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="1">
+        <v>9.79</v>
+      </c>
+      <c r="D43" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.29</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="1">
+        <v>13.95</v>
+      </c>
+      <c r="D44" s="1">
+        <v>13.68</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="1">
+        <v>13.68</v>
+      </c>
+      <c r="H44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="1">
+        <v>13.95</v>
+      </c>
+      <c r="D45" s="1">
+        <v>13.68</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="F45" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="1">
+        <v>13.68</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D46" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F46" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F47" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F48" t="s">
+        <v>104</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F49" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F50" t="s">
+        <v>104</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F51" t="s">
+        <v>104</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F52" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F53" t="s">
+        <v>104</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F54" t="s">
+        <v>104</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F56" t="s">
+        <v>104</v>
+      </c>
+      <c r="G56" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>104</v>
+      </c>
+      <c r="G57" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>104</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D59" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>104</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D60" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>104</v>
+      </c>
+      <c r="G60" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D61" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>104</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D62" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D63" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D64" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G64" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>141</v>
+      </c>
+      <c r="B65" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F65" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C66" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F66" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="1">
+        <v>12.75</v>
+      </c>
+      <c r="D67" s="1">
+        <v>12.51</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="F67" t="s">
+        <v>43</v>
+      </c>
+      <c r="G67" s="1">
+        <v>12.51</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" t="s">
+        <v>148</v>
+      </c>
+      <c r="C68" s="1">
         <v>12.19</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D68" s="1">
         <v>12.12</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E68" s="1">
         <v>0.07</v>
       </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="F68" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="1">
         <v>12.12</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" s="1">
+        <v>11.59</v>
+      </c>
+      <c r="D69" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F69" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69" s="1">
+        <v>11.54</v>
+      </c>
+      <c r="H69" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-NL-2026-05-16.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="158">
   <si>
     <t>Product</t>
   </si>
@@ -49,6 +49,15 @@
     <t>FBR</t>
   </si>
   <si>
+    <t>Sentio Let The Party Begin miniparfum eau de parfum for unisex 15ml</t>
+  </si>
+  <si>
+    <t>7640158817810</t>
+  </si>
+  <si>
+    <t>TM BOOKS</t>
+  </si>
+  <si>
     <t>Omerta - Royal X - Eau de toilette - 100ML</t>
   </si>
   <si>
@@ -106,67 +115,67 @@
     <t>8720938379314</t>
   </si>
   <si>
+    <t>Azira - Royal Oud - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102720</t>
+  </si>
+  <si>
+    <t>Dorsh</t>
+  </si>
+  <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Hello Kitty - Giftset - Unicorn Rainbow - Showergel + Water-Based Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>7640158816998</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102706</t>
+  </si>
+  <si>
     <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>6291012000261</t>
   </si>
   <si>
-    <t>Dorsh</t>
-  </si>
-  <si>
-    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
-  </si>
-  <si>
-    <t>5414666014427</t>
-  </si>
-  <si>
-    <t>Juwelium</t>
-  </si>
-  <si>
-    <t>Azira - Royal Oud - Eau de Parfum Unisex</t>
-  </si>
-  <si>
-    <t>8721349102720</t>
-  </si>
-  <si>
-    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
-  </si>
-  <si>
-    <t>8721349102706</t>
-  </si>
-  <si>
-    <t>Hello Kitty Rainbow Eau de Parfum voor Kinderen 50ml</t>
-  </si>
-  <si>
-    <t>8721055493297</t>
-  </si>
-  <si>
-    <t>Koopjesfun.nl</t>
-  </si>
-  <si>
-    <t>Sentio Vintage Forrest Unisex Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8721055491477</t>
-  </si>
-  <si>
     <t>Sentio What Happens Under The Mistletoe Stays Under The Mistletoe - Eau de parfum</t>
   </si>
   <si>
     <t>8721055492795</t>
   </si>
   <si>
+    <t>Dorall Twilight Wilderness - Herenparfum eau de toilette - 100 ml</t>
+  </si>
+  <si>
+    <t>6291012874381</t>
+  </si>
+  <si>
     <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
   </si>
   <si>
     <t>8719214757229</t>
   </si>
   <si>
-    <t>NG Embodiment of Style Women Eau de Parfum Spray 100 ml</t>
-  </si>
-  <si>
-    <t>8719214752576</t>
+    <t>Hello Kitty Kisses Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>8721055493273</t>
   </si>
   <si>
     <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
@@ -307,16 +316,28 @@
     <t>8715658380580</t>
   </si>
   <si>
-    <t>Real Time - Oú sont les - Eau de parfum - 100 ml</t>
-  </si>
-  <si>
-    <t>8715658361466</t>
-  </si>
-  <si>
-    <t>Omerta - Angelina - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997764</t>
+    <t>Omerta Body Survival For Man - Eau de Toilette voor heren - 100ML</t>
+  </si>
+  <si>
+    <t>8715658998471</t>
+  </si>
+  <si>
+    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658997443</t>
+  </si>
+  <si>
+    <t>Hello Kitty Googly Line Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
+    <t>7640158816899</t>
+  </si>
+  <si>
+    <t>Dorall Quaint damesparfum eau de toilette 100 ml</t>
+  </si>
+  <si>
+    <t>6291012905399</t>
   </si>
   <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
@@ -334,6 +355,12 @@
     <t>8721055494225</t>
   </si>
   <si>
+    <t>Real Time - Free Sky For Woman - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658002512</t>
+  </si>
+  <si>
     <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -448,22 +475,16 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Omerta Black &amp; Silver Man Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658998464</t>
-  </si>
-  <si>
-    <t>Sentio Love &amp; Casual for Him Eau de Toilette Spray 100 ml</t>
-  </si>
-  <si>
-    <t>8721055493723</t>
-  </si>
-  <si>
-    <t>Real Time - Fine Gold Pink Vibrations - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658361015</t>
+    <t>Bubble Bliss Unicorn Giftbook Parfum Dreamy Glitterwings EDP voor meisjes 50ml</t>
+  </si>
+  <si>
+    <t>8721055492245</t>
+  </si>
+  <si>
+    <t>Real Time Coup d'Amour eau de parfum 100 ml.</t>
+  </si>
+  <si>
+    <t>8715658360063</t>
   </si>
 </sst>
 </file>
@@ -855,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -928,19 +949,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>11.5</v>
+        <v>10.49</v>
       </c>
       <c r="D3" s="1">
-        <v>9.99</v>
+        <v>8.5</v>
       </c>
       <c r="E3" s="1">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>9.99</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -948,25 +969,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>17.45</v>
+        <v>11.5</v>
       </c>
       <c r="D4" s="1">
-        <v>15.95</v>
+        <v>9.99</v>
       </c>
       <c r="E4" s="1">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>15.95</v>
+        <v>9.99</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -980,16 +1001,16 @@
         <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>16.95</v>
+        <v>17.45</v>
       </c>
       <c r="D5" s="1">
         <v>15.95</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
         <v>15.95</v>
@@ -1000,10 +1021,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>16.95</v>
@@ -1015,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
         <v>15.95</v>
@@ -1026,10 +1047,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>16.95</v>
@@ -1041,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1">
         <v>15.95</v>
@@ -1052,10 +1073,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>16.95</v>
@@ -1067,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1">
         <v>15.95</v>
@@ -1078,10 +1099,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
         <v>16.95</v>
@@ -1093,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1">
         <v>15.95</v>
@@ -1104,10 +1125,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>16.95</v>
@@ -1119,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
         <v>15.95</v>
@@ -1130,22 +1151,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
-        <v>16.89</v>
+        <v>16.95</v>
       </c>
       <c r="D11" s="1">
         <v>15.95</v>
       </c>
       <c r="E11" s="1">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
         <v>15.95</v>
@@ -1156,25 +1177,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
-        <v>9.79</v>
+        <v>16.89</v>
       </c>
       <c r="D12" s="1">
-        <v>9.31</v>
+        <v>15.95</v>
       </c>
       <c r="E12" s="1">
-        <v>0.48</v>
+        <v>0.94</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>9.31</v>
+        <v>15.95</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1188,19 +1209,19 @@
         <v>35</v>
       </c>
       <c r="C13" s="1">
-        <v>9.94</v>
+        <v>14.05</v>
       </c>
       <c r="D13" s="1">
-        <v>9.48</v>
+        <v>13.49</v>
       </c>
       <c r="E13" s="1">
-        <v>0.46</v>
+        <v>0.56</v>
       </c>
       <c r="F13" t="s">
         <v>36</v>
       </c>
       <c r="G13" s="1">
-        <v>9.48</v>
+        <v>13.49</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1214,19 +1235,19 @@
         <v>38</v>
       </c>
       <c r="C14" s="1">
-        <v>14.05</v>
+        <v>9.94</v>
       </c>
       <c r="D14" s="1">
-        <v>13.66</v>
+        <v>9.48</v>
       </c>
       <c r="E14" s="1">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
-        <v>13.66</v>
+        <v>9.48</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1234,25 +1255,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1">
-        <v>14.25</v>
+        <v>16.95</v>
       </c>
       <c r="D15" s="1">
-        <v>13.91</v>
+        <v>16.51</v>
       </c>
       <c r="E15" s="1">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1">
-        <v>13.91</v>
+        <v>16.51</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1260,25 +1281,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1">
-        <v>13.95</v>
+        <v>14.25</v>
       </c>
       <c r="D16" s="1">
-        <v>13.62</v>
+        <v>13.91</v>
       </c>
       <c r="E16" s="1">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1">
-        <v>13.62</v>
+        <v>13.91</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1286,25 +1307,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1">
-        <v>13.89</v>
+        <v>9.79</v>
       </c>
       <c r="D17" s="1">
-        <v>13.56</v>
+        <v>9.45</v>
       </c>
       <c r="E17" s="1">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
-        <v>13.56</v>
+        <v>9.45</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1312,10 +1333,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1">
         <v>8.25</v>
@@ -1327,7 +1348,7 @@
         <v>0.33</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18" s="1">
         <v>7.92</v>
@@ -1338,25 +1359,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1">
-        <v>9.79</v>
+        <v>14.59</v>
       </c>
       <c r="D19" s="1">
-        <v>9.47</v>
+        <v>14.26</v>
       </c>
       <c r="E19" s="1">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G19" s="1">
-        <v>9.47</v>
+        <v>14.26</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -1364,25 +1385,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1">
-        <v>12.5</v>
+        <v>9.79</v>
       </c>
       <c r="D20" s="1">
-        <v>12.2</v>
+        <v>9.47</v>
       </c>
       <c r="E20" s="1">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1">
-        <v>12.2</v>
+        <v>9.47</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1390,25 +1411,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1">
-        <v>9.79</v>
+        <v>13.95</v>
       </c>
       <c r="D21" s="1">
-        <v>9.5</v>
+        <v>13.64</v>
       </c>
       <c r="E21" s="1">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G21" s="1">
-        <v>9.5</v>
+        <v>13.64</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1416,10 +1437,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1">
         <v>9.79</v>
@@ -1431,7 +1452,7 @@
         <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
         <v>9.5</v>
@@ -1442,10 +1463,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1">
         <v>9.79</v>
@@ -1457,7 +1478,7 @@
         <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1">
         <v>9.5</v>
@@ -1468,10 +1489,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1">
         <v>9.79</v>
@@ -1483,7 +1504,7 @@
         <v>0.29</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
         <v>9.5</v>
@@ -1494,10 +1515,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1">
         <v>9.79</v>
@@ -1509,7 +1530,7 @@
         <v>0.29</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
         <v>9.5</v>
@@ -1520,10 +1541,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1">
         <v>9.79</v>
@@ -1535,7 +1556,7 @@
         <v>0.29</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1">
         <v>9.5</v>
@@ -1546,10 +1567,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1">
         <v>9.79</v>
@@ -1561,7 +1582,7 @@
         <v>0.29</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1">
         <v>9.5</v>
@@ -1572,10 +1593,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1">
         <v>9.79</v>
@@ -1587,7 +1608,7 @@
         <v>0.29</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
         <v>9.5</v>
@@ -1598,10 +1619,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1">
         <v>9.79</v>
@@ -1613,7 +1634,7 @@
         <v>0.29</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G29" s="1">
         <v>9.5</v>
@@ -1624,10 +1645,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1">
         <v>9.79</v>
@@ -1639,7 +1660,7 @@
         <v>0.29</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1">
         <v>9.5</v>
@@ -1650,10 +1671,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1">
         <v>9.79</v>
@@ -1665,7 +1686,7 @@
         <v>0.29</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
         <v>9.5</v>
@@ -1676,10 +1697,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1">
         <v>9.79</v>
@@ -1691,7 +1712,7 @@
         <v>0.29</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1">
         <v>9.5</v>
@@ -1702,10 +1723,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1">
         <v>9.79</v>
@@ -1717,7 +1738,7 @@
         <v>0.29</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G33" s="1">
         <v>9.5</v>
@@ -1728,10 +1749,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1">
         <v>9.79</v>
@@ -1743,7 +1764,7 @@
         <v>0.29</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G34" s="1">
         <v>9.5</v>
@@ -1754,10 +1775,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1">
         <v>9.79</v>
@@ -1769,7 +1790,7 @@
         <v>0.29</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G35" s="1">
         <v>9.5</v>
@@ -1780,10 +1801,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1">
         <v>9.79</v>
@@ -1795,7 +1816,7 @@
         <v>0.29</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G36" s="1">
         <v>9.5</v>
@@ -1806,10 +1827,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1">
         <v>9.79</v>
@@ -1821,7 +1842,7 @@
         <v>0.29</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G37" s="1">
         <v>9.5</v>
@@ -1832,10 +1853,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1">
         <v>9.79</v>
@@ -1847,7 +1868,7 @@
         <v>0.29</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G38" s="1">
         <v>9.5</v>
@@ -1858,10 +1879,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" s="1">
         <v>9.79</v>
@@ -1873,7 +1894,7 @@
         <v>0.29</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G39" s="1">
         <v>9.5</v>
@@ -1884,10 +1905,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1">
         <v>9.79</v>
@@ -1899,7 +1920,7 @@
         <v>0.29</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G40" s="1">
         <v>9.5</v>
@@ -1910,10 +1931,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" s="1">
         <v>9.79</v>
@@ -1925,7 +1946,7 @@
         <v>0.29</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G41" s="1">
         <v>9.5</v>
@@ -1936,10 +1957,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="1">
         <v>9.79</v>
@@ -1951,7 +1972,7 @@
         <v>0.29</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1">
         <v>9.5</v>
@@ -1962,10 +1983,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1">
         <v>9.79</v>
@@ -1977,7 +1998,7 @@
         <v>0.29</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1">
         <v>9.5</v>
@@ -1988,25 +2009,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="1">
-        <v>13.95</v>
+        <v>9.79</v>
       </c>
       <c r="D44" s="1">
-        <v>13.68</v>
+        <v>9.5</v>
       </c>
       <c r="E44" s="1">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1">
-        <v>13.68</v>
+        <v>9.5</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2014,10 +2035,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="1">
         <v>13.95</v>
@@ -2029,7 +2050,7 @@
         <v>0.27</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G45" s="1">
         <v>13.68</v>
@@ -2040,25 +2061,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1">
-        <v>5.25</v>
+        <v>13.99</v>
       </c>
       <c r="D46" s="1">
-        <v>4.99</v>
+        <v>13.72</v>
       </c>
       <c r="E46" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="F46" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G46" s="1">
-        <v>4.99</v>
+        <v>13.72</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2072,19 +2093,19 @@
         <v>106</v>
       </c>
       <c r="C47" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D47" s="1">
-        <v>4.99</v>
+        <v>13.68</v>
       </c>
       <c r="E47" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="F47" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G47" s="1">
-        <v>4.99</v>
+        <v>13.68</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2098,19 +2119,19 @@
         <v>108</v>
       </c>
       <c r="C48" s="1">
-        <v>5.25</v>
+        <v>13.95</v>
       </c>
       <c r="D48" s="1">
-        <v>4.99</v>
+        <v>13.68</v>
       </c>
       <c r="E48" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G48" s="1">
-        <v>4.99</v>
+        <v>13.68</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2133,7 +2154,7 @@
         <v>0.26</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G49" s="1">
         <v>4.99</v>
@@ -2144,10 +2165,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C50" s="1">
         <v>5.25</v>
@@ -2159,7 +2180,7 @@
         <v>0.26</v>
       </c>
       <c r="F50" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G50" s="1">
         <v>4.99</v>
@@ -2170,25 +2191,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C51" s="1">
-        <v>5.25</v>
+        <v>11.95</v>
       </c>
       <c r="D51" s="1">
-        <v>4.99</v>
+        <v>11.69</v>
       </c>
       <c r="E51" s="1">
         <v>0.26</v>
       </c>
       <c r="F51" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G51" s="1">
-        <v>4.99</v>
+        <v>11.69</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2196,10 +2217,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="1">
         <v>5.25</v>
@@ -2211,7 +2232,7 @@
         <v>0.26</v>
       </c>
       <c r="F52" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G52" s="1">
         <v>4.99</v>
@@ -2222,10 +2243,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C53" s="1">
         <v>5.25</v>
@@ -2237,7 +2258,7 @@
         <v>0.26</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G53" s="1">
         <v>4.99</v>
@@ -2248,10 +2269,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C54" s="1">
         <v>5.25</v>
@@ -2263,7 +2284,7 @@
         <v>0.26</v>
       </c>
       <c r="F54" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G54" s="1">
         <v>4.99</v>
@@ -2274,10 +2295,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C55" s="1">
         <v>5.25</v>
@@ -2289,7 +2310,7 @@
         <v>0.26</v>
       </c>
       <c r="F55" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G55" s="1">
         <v>4.99</v>
@@ -2300,10 +2321,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C56" s="1">
         <v>5.25</v>
@@ -2315,7 +2336,7 @@
         <v>0.26</v>
       </c>
       <c r="F56" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G56" s="1">
         <v>4.99</v>
@@ -2326,10 +2347,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C57" s="1">
         <v>5.25</v>
@@ -2341,7 +2362,7 @@
         <v>0.26</v>
       </c>
       <c r="F57" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G57" s="1">
         <v>4.99</v>
@@ -2352,10 +2373,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C58" s="1">
         <v>5.25</v>
@@ -2367,7 +2388,7 @@
         <v>0.26</v>
       </c>
       <c r="F58" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G58" s="1">
         <v>4.99</v>
@@ -2378,10 +2399,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C59" s="1">
         <v>5.25</v>
@@ -2393,7 +2414,7 @@
         <v>0.26</v>
       </c>
       <c r="F59" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G59" s="1">
         <v>4.99</v>
@@ -2404,10 +2425,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" s="1">
         <v>5.25</v>
@@ -2419,7 +2440,7 @@
         <v>0.26</v>
       </c>
       <c r="F60" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G60" s="1">
         <v>4.99</v>
@@ -2430,10 +2451,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C61" s="1">
         <v>5.25</v>
@@ -2445,7 +2466,7 @@
         <v>0.26</v>
       </c>
       <c r="F61" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G61" s="1">
         <v>4.99</v>
@@ -2456,10 +2477,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="1">
         <v>5.25</v>
@@ -2471,7 +2492,7 @@
         <v>0.26</v>
       </c>
       <c r="F62" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G62" s="1">
         <v>4.99</v>
@@ -2482,10 +2503,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C63" s="1">
         <v>5.25</v>
@@ -2497,7 +2518,7 @@
         <v>0.26</v>
       </c>
       <c r="F63" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G63" s="1">
         <v>4.99</v>
@@ -2508,10 +2529,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C64" s="1">
         <v>5.25</v>
@@ -2523,7 +2544,7 @@
         <v>0.26</v>
       </c>
       <c r="F64" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G64" s="1">
         <v>4.99</v>
@@ -2534,10 +2555,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C65" s="1">
         <v>5.25</v>
@@ -2549,7 +2570,7 @@
         <v>0.26</v>
       </c>
       <c r="F65" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G65" s="1">
         <v>4.99</v>
@@ -2560,10 +2581,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C66" s="1">
         <v>5.25</v>
@@ -2575,7 +2596,7 @@
         <v>0.26</v>
       </c>
       <c r="F66" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G66" s="1">
         <v>4.99</v>
@@ -2586,25 +2607,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C67" s="1">
-        <v>12.75</v>
+        <v>5.25</v>
       </c>
       <c r="D67" s="1">
-        <v>12.51</v>
+        <v>4.99</v>
       </c>
       <c r="E67" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="G67" s="1">
-        <v>12.51</v>
+        <v>4.99</v>
       </c>
       <c r="H67" t="s">
         <v>11</v>
@@ -2612,25 +2633,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C68" s="1">
-        <v>12.19</v>
+        <v>5.25</v>
       </c>
       <c r="D68" s="1">
-        <v>12.12</v>
+        <v>4.99</v>
       </c>
       <c r="E68" s="1">
-        <v>0.07</v>
+        <v>0.26</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="G68" s="1">
-        <v>12.12</v>
+        <v>4.99</v>
       </c>
       <c r="H68" t="s">
         <v>11</v>
@@ -2638,27 +2659,105 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C69" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F69" t="s">
+        <v>111</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D70" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F70" t="s">
+        <v>111</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="H70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="1">
+        <v>13.95</v>
+      </c>
+      <c r="D71" s="1">
+        <v>13.7</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="F71" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="1">
+        <v>13.7</v>
+      </c>
+      <c r="H71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" t="s">
+        <v>157</v>
+      </c>
+      <c r="C72" s="1">
         <v>11.59</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D72" s="1">
         <v>11.54</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E72" s="1">
         <v>0.05</v>
       </c>
-      <c r="F69" t="s">
-        <v>43</v>
-      </c>
-      <c r="G69" s="1">
+      <c r="F72" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="1">
         <v>11.54</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H72" t="s">
         <v>11</v>
       </c>
     </row>
